--- a/research/traditional_assets/database/data/argentina/argentina_chemical_specialty.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_chemical_specialty.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.2361461301589003</v>
+        <v>0.2353488687033442</v>
       </c>
       <c r="C2">
-        <v>649.7321327681395</v>
+        <v>645.8421139279072</v>
       </c>
       <c r="D2">
-        <v>617.4321327681396</v>
+        <v>620.0291139279072</v>
       </c>
       <c r="E2">
-        <v>-266.6</v>
+        <v>-260.113</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>6.487000000000001</v>
       </c>
       <c r="G2">
         <v>32.3</v>
@@ -1451,28 +1451,28 @@
         <v>59.2</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3262961</v>
       </c>
       <c r="N2">
-        <v>59.2</v>
+        <v>58.8737039</v>
       </c>
       <c r="O2">
-        <v>20.72</v>
+        <v>20.605796365</v>
       </c>
       <c r="P2">
-        <v>38.48</v>
+        <v>38.26790753500001</v>
       </c>
       <c r="Q2">
-        <v>56.48</v>
+        <v>56.26790753500001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.2361461301589003</v>
+        <v>0.2373958774781254</v>
       </c>
       <c r="T2">
-        <v>0.9352413814778209</v>
+        <v>0.9413818551945945</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>181.4303021090353</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.2353488687033442</v>
+        <v>0.234551607247788</v>
       </c>
       <c r="C3">
-        <v>645.8421139279072</v>
+        <v>641.9740336874005</v>
       </c>
       <c r="D3">
-        <v>620.0291139279072</v>
+        <v>622.6480336874006</v>
       </c>
       <c r="E3">
-        <v>-260.113</v>
+        <v>-253.626</v>
       </c>
       <c r="F3">
-        <v>6.487000000000001</v>
+        <v>12.974</v>
       </c>
       <c r="G3">
         <v>32.3</v>
@@ -1533,28 +1533,28 @@
         <v>59.2</v>
       </c>
       <c r="M3">
-        <v>0.3262961</v>
+        <v>0.6525922000000001</v>
       </c>
       <c r="N3">
-        <v>58.8737039</v>
+        <v>58.5474078</v>
       </c>
       <c r="O3">
-        <v>20.605796365</v>
+        <v>20.49159273</v>
       </c>
       <c r="P3">
-        <v>38.26790753500001</v>
+        <v>38.05581507</v>
       </c>
       <c r="Q3">
-        <v>56.26790753500001</v>
+        <v>56.05581507</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.2373958774781254</v>
+        <v>0.2386711298446816</v>
       </c>
       <c r="T3">
-        <v>0.9413818551945945</v>
+        <v>0.9476476447015063</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>181.4303021090353</v>
+        <v>90.71515105451765</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.234551607247788</v>
+        <v>0.2337543457922318</v>
       </c>
       <c r="C4">
-        <v>641.9740336874005</v>
+        <v>638.1281712229249</v>
       </c>
       <c r="D4">
-        <v>622.6480336874006</v>
+        <v>625.289171222925</v>
       </c>
       <c r="E4">
-        <v>-253.626</v>
+        <v>-247.139</v>
       </c>
       <c r="F4">
-        <v>12.974</v>
+        <v>19.461</v>
       </c>
       <c r="G4">
         <v>32.3</v>
@@ -1615,28 +1615,28 @@
         <v>59.2</v>
       </c>
       <c r="M4">
-        <v>0.6525922000000001</v>
+        <v>0.9788883</v>
       </c>
       <c r="N4">
-        <v>58.5474078</v>
+        <v>58.2211117</v>
       </c>
       <c r="O4">
-        <v>20.49159273</v>
+        <v>20.377389095</v>
       </c>
       <c r="P4">
-        <v>38.05581507</v>
+        <v>37.843722605</v>
       </c>
       <c r="Q4">
-        <v>56.05581507</v>
+        <v>55.843722605</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.2386711298446816</v>
+        <v>0.2399726760744658</v>
       </c>
       <c r="T4">
-        <v>0.9476476447015063</v>
+        <v>0.9540426257446429</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>90.71515105451765</v>
+        <v>60.47676736967844</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.2337543457922318</v>
+        <v>0.2329570843366757</v>
       </c>
       <c r="C5">
-        <v>638.1281712229249</v>
+        <v>634.3048104677848</v>
       </c>
       <c r="D5">
-        <v>625.289171222925</v>
+        <v>627.9528104677848</v>
       </c>
       <c r="E5">
-        <v>-247.139</v>
+        <v>-240.652</v>
       </c>
       <c r="F5">
-        <v>19.461</v>
+        <v>25.948</v>
       </c>
       <c r="G5">
         <v>32.3</v>
@@ -1697,28 +1697,28 @@
         <v>59.2</v>
       </c>
       <c r="M5">
-        <v>0.9788883</v>
+        <v>1.3051844</v>
       </c>
       <c r="N5">
-        <v>58.2211117</v>
+        <v>57.8948156</v>
       </c>
       <c r="O5">
-        <v>20.377389095</v>
+        <v>20.26318546</v>
       </c>
       <c r="P5">
-        <v>37.843722605</v>
+        <v>37.63163014</v>
       </c>
       <c r="Q5">
-        <v>55.843722605</v>
+        <v>55.63163014</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.2399726760744658</v>
+        <v>0.2413013378507038</v>
       </c>
       <c r="T5">
-        <v>0.9540426257446429</v>
+        <v>0.9605708355595118</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>60.47676736967844</v>
+        <v>45.35757552725882</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.2329570843366757</v>
+        <v>0.2321598228811195</v>
       </c>
       <c r="C6">
-        <v>634.3048104677848</v>
+        <v>630.5042402140368</v>
       </c>
       <c r="D6">
-        <v>627.9528104677848</v>
+        <v>630.6392402140369</v>
       </c>
       <c r="E6">
-        <v>-240.652</v>
+        <v>-234.165</v>
       </c>
       <c r="F6">
-        <v>25.948</v>
+        <v>32.435</v>
       </c>
       <c r="G6">
         <v>32.3</v>
@@ -1779,28 +1779,28 @@
         <v>59.2</v>
       </c>
       <c r="M6">
-        <v>1.3051844</v>
+        <v>1.6314805</v>
       </c>
       <c r="N6">
-        <v>57.8948156</v>
+        <v>57.5685195</v>
       </c>
       <c r="O6">
-        <v>20.26318546</v>
+        <v>20.148981825</v>
       </c>
       <c r="P6">
-        <v>37.63163014</v>
+        <v>37.419537675</v>
       </c>
       <c r="Q6">
-        <v>55.63163014</v>
+        <v>55.419537675</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.2413013378507038</v>
+        <v>0.24265797145381</v>
       </c>
       <c r="T6">
-        <v>0.9605708355595118</v>
+        <v>0.9672364813704831</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>45.35757552725882</v>
+        <v>36.28606042180706</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.2321598228811195</v>
+        <v>0.2313625614255634</v>
       </c>
       <c r="C7">
-        <v>630.5042402140368</v>
+        <v>626.7267542168685</v>
       </c>
       <c r="D7">
-        <v>630.6392402140369</v>
+        <v>633.3487542168685</v>
       </c>
       <c r="E7">
-        <v>-234.165</v>
+        <v>-227.678</v>
       </c>
       <c r="F7">
-        <v>32.435</v>
+        <v>38.922</v>
       </c>
       <c r="G7">
         <v>32.3</v>
@@ -1861,28 +1861,28 @@
         <v>59.2</v>
       </c>
       <c r="M7">
-        <v>1.6314805</v>
+        <v>1.9577766</v>
       </c>
       <c r="N7">
-        <v>57.5685195</v>
+        <v>57.2422234</v>
       </c>
       <c r="O7">
-        <v>20.148981825</v>
+        <v>20.03477819</v>
       </c>
       <c r="P7">
-        <v>37.419537675</v>
+        <v>37.20744521</v>
       </c>
       <c r="Q7">
-        <v>55.419537675</v>
+        <v>55.20744521</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.24265797145381</v>
+        <v>0.2440434696016632</v>
       </c>
       <c r="T7">
-        <v>0.9672364813704831</v>
+        <v>0.9740439494327517</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>36.28606042180706</v>
+        <v>30.23838368483922</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.2313625614255634</v>
+        <v>0.2305652999700073</v>
       </c>
       <c r="C8">
-        <v>626.7267542168685</v>
+        <v>622.9726513016759</v>
       </c>
       <c r="D8">
-        <v>633.3487542168685</v>
+        <v>636.0816513016759</v>
       </c>
       <c r="E8">
-        <v>-227.678</v>
+        <v>-221.191</v>
       </c>
       <c r="F8">
-        <v>38.922</v>
+        <v>45.409</v>
       </c>
       <c r="G8">
         <v>32.3</v>
@@ -1943,28 +1943,28 @@
         <v>59.2</v>
       </c>
       <c r="M8">
-        <v>1.9577766</v>
+        <v>2.2840727</v>
       </c>
       <c r="N8">
-        <v>57.2422234</v>
+        <v>56.9159273</v>
       </c>
       <c r="O8">
-        <v>20.03477819</v>
+        <v>19.920574555</v>
       </c>
       <c r="P8">
-        <v>37.20744521</v>
+        <v>36.99535274500001</v>
       </c>
       <c r="Q8">
-        <v>55.20744521</v>
+        <v>54.99535274500001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.2440434696016632</v>
+        <v>0.2454587634086099</v>
       </c>
       <c r="T8">
-        <v>0.9740439494327517</v>
+        <v>0.9809978146576497</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>30.23838368483922</v>
+        <v>25.91861458700505</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.2305652999700072</v>
+        <v>0.2297680385144511</v>
       </c>
       <c r="C9">
-        <v>622.972651301676</v>
+        <v>619.2422354739289</v>
       </c>
       <c r="D9">
-        <v>636.0816513016761</v>
+        <v>638.8382354739289</v>
       </c>
       <c r="E9">
-        <v>-221.191</v>
+        <v>-214.704</v>
       </c>
       <c r="F9">
-        <v>45.40900000000001</v>
+        <v>51.89600000000001</v>
       </c>
       <c r="G9">
         <v>32.3</v>
@@ -2025,28 +2025,28 @@
         <v>59.2</v>
       </c>
       <c r="M9">
-        <v>2.2840727</v>
+        <v>2.6103688</v>
       </c>
       <c r="N9">
-        <v>56.9159273</v>
+        <v>56.5896312</v>
       </c>
       <c r="O9">
-        <v>19.920574555</v>
+        <v>19.80637092</v>
       </c>
       <c r="P9">
-        <v>36.99535274500001</v>
+        <v>36.78326028</v>
       </c>
       <c r="Q9">
-        <v>54.99535274500001</v>
+        <v>54.78326028</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.2454587634086099</v>
+        <v>0.2469048244722294</v>
       </c>
       <c r="T9">
-        <v>0.9809978146576497</v>
+        <v>0.9881028508656976</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>25.91861458700504</v>
+        <v>22.67878776362941</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.2297680385144511</v>
+        <v>0.228970777058895</v>
       </c>
       <c r="C10">
-        <v>619.2422354739289</v>
+        <v>615.5358160319023</v>
       </c>
       <c r="D10">
-        <v>638.8382354739289</v>
+        <v>641.6188160319024</v>
       </c>
       <c r="E10">
-        <v>-214.704</v>
+        <v>-208.217</v>
       </c>
       <c r="F10">
-        <v>51.89600000000001</v>
+        <v>58.383</v>
       </c>
       <c r="G10">
         <v>32.3</v>
@@ -2107,28 +2107,28 @@
         <v>59.2</v>
       </c>
       <c r="M10">
-        <v>2.6103688</v>
+        <v>2.9366649</v>
       </c>
       <c r="N10">
-        <v>56.5896312</v>
+        <v>56.26333510000001</v>
       </c>
       <c r="O10">
-        <v>19.80637092</v>
+        <v>19.692167285</v>
       </c>
       <c r="P10">
-        <v>36.78326028</v>
+        <v>36.57116781500001</v>
       </c>
       <c r="Q10">
-        <v>54.78326028</v>
+        <v>54.57116781500001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2469048244722294</v>
+        <v>0.2483826670976868</v>
       </c>
       <c r="T10">
-        <v>0.9881028508656976</v>
+        <v>0.9953640417156808</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>22.67878776362941</v>
+        <v>20.15892245655948</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.228970777058895</v>
+        <v>0.2281735156033388</v>
       </c>
       <c r="C11">
-        <v>615.5358160319023</v>
+        <v>611.8537076823676</v>
       </c>
       <c r="D11">
-        <v>641.6188160319024</v>
+        <v>644.4237076823676</v>
       </c>
       <c r="E11">
-        <v>-208.217</v>
+        <v>-201.73</v>
       </c>
       <c r="F11">
-        <v>58.383</v>
+        <v>64.87</v>
       </c>
       <c r="G11">
         <v>32.3</v>
@@ -2189,28 +2189,28 @@
         <v>59.2</v>
       </c>
       <c r="M11">
-        <v>2.9366649</v>
+        <v>3.262961</v>
       </c>
       <c r="N11">
-        <v>56.26333510000001</v>
+        <v>55.93703900000001</v>
       </c>
       <c r="O11">
-        <v>19.692167285</v>
+        <v>19.57796365</v>
       </c>
       <c r="P11">
-        <v>36.57116781500001</v>
+        <v>36.35907535</v>
       </c>
       <c r="Q11">
-        <v>54.57116781500001</v>
+        <v>54.35907535</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2483826670976868</v>
+        <v>0.2498933506703764</v>
       </c>
       <c r="T11">
-        <v>0.9953640417156808</v>
+        <v>1.00278659236233</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>20.15892245655948</v>
+        <v>18.14303021090353</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.2281735156033388</v>
+        <v>0.2273762541477827</v>
       </c>
       <c r="C12">
-        <v>611.8537076823676</v>
+        <v>608.1962306593289</v>
       </c>
       <c r="D12">
-        <v>644.4237076823676</v>
+        <v>647.2532306593289</v>
       </c>
       <c r="E12">
-        <v>-201.73</v>
+        <v>-195.243</v>
       </c>
       <c r="F12">
-        <v>64.87</v>
+        <v>71.357</v>
       </c>
       <c r="G12">
         <v>32.3</v>
@@ -2271,28 +2271,28 @@
         <v>59.2</v>
       </c>
       <c r="M12">
-        <v>3.262961</v>
+        <v>3.5892571</v>
       </c>
       <c r="N12">
-        <v>55.93703900000001</v>
+        <v>55.61074290000001</v>
       </c>
       <c r="O12">
-        <v>19.57796365</v>
+        <v>19.463760015</v>
       </c>
       <c r="P12">
-        <v>36.35907535</v>
+        <v>36.146982885</v>
       </c>
       <c r="Q12">
-        <v>54.35907535</v>
+        <v>54.146982885</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2498933506703764</v>
+        <v>0.2514379821885199</v>
       </c>
       <c r="T12">
-        <v>1.00278659236233</v>
+        <v>1.010375941899916</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.14303021090353</v>
+        <v>16.49366382809412</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.2273762541477827</v>
+        <v>0.2265789926922264</v>
       </c>
       <c r="C13">
-        <v>608.1962306593289</v>
+        <v>604.5637108459038</v>
       </c>
       <c r="D13">
-        <v>647.2532306593289</v>
+        <v>650.1077108459039</v>
       </c>
       <c r="E13">
-        <v>-195.243</v>
+        <v>-188.756</v>
       </c>
       <c r="F13">
-        <v>71.357</v>
+        <v>77.84400000000001</v>
       </c>
       <c r="G13">
         <v>32.3</v>
@@ -2353,28 +2353,28 @@
         <v>59.2</v>
       </c>
       <c r="M13">
-        <v>3.5892571</v>
+        <v>3.9155532</v>
       </c>
       <c r="N13">
-        <v>55.61074290000001</v>
+        <v>55.2844468</v>
       </c>
       <c r="O13">
-        <v>19.463760015</v>
+        <v>19.34955638</v>
       </c>
       <c r="P13">
-        <v>36.146982885</v>
+        <v>35.93489042</v>
       </c>
       <c r="Q13">
-        <v>54.146982885</v>
+        <v>53.93489042</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2514379821885199</v>
+        <v>0.2530177189684392</v>
       </c>
       <c r="T13">
-        <v>1.010375941899916</v>
+        <v>1.018137776654264</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.49366382809412</v>
+        <v>15.11919184241961</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.2265789926922264</v>
+        <v>0.2257817312366703</v>
       </c>
       <c r="C14">
-        <v>604.5637108459038</v>
+        <v>600.9564798994403</v>
       </c>
       <c r="D14">
-        <v>650.1077108459039</v>
+        <v>652.9874798994404</v>
       </c>
       <c r="E14">
-        <v>-188.756</v>
+        <v>-182.269</v>
       </c>
       <c r="F14">
-        <v>77.84400000000001</v>
+        <v>84.331</v>
       </c>
       <c r="G14">
         <v>32.3</v>
@@ -2435,28 +2435,28 @@
         <v>59.2</v>
       </c>
       <c r="M14">
-        <v>3.9155532</v>
+        <v>4.2418493</v>
       </c>
       <c r="N14">
-        <v>55.2844468</v>
+        <v>54.9581507</v>
       </c>
       <c r="O14">
-        <v>19.34955638</v>
+        <v>19.235352745</v>
       </c>
       <c r="P14">
-        <v>35.93489042</v>
+        <v>35.722797955</v>
       </c>
       <c r="Q14">
-        <v>53.93489042</v>
+        <v>53.722797955</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2530177189684392</v>
+        <v>0.2546337715364027</v>
       </c>
       <c r="T14">
-        <v>1.018137776654264</v>
+        <v>1.026078044391471</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.11919184241961</v>
+        <v>13.95617708531041</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.2257817312366703</v>
+        <v>0.2249844697811142</v>
       </c>
       <c r="C15">
-        <v>600.9564798994403</v>
+        <v>597.3748753799775</v>
       </c>
       <c r="D15">
-        <v>652.9874798994404</v>
+        <v>655.8928753799776</v>
       </c>
       <c r="E15">
-        <v>-182.269</v>
+        <v>-175.782</v>
       </c>
       <c r="F15">
-        <v>84.331</v>
+        <v>90.81800000000001</v>
       </c>
       <c r="G15">
         <v>32.3</v>
@@ -2517,28 +2517,28 @@
         <v>59.2</v>
       </c>
       <c r="M15">
-        <v>4.2418493</v>
+        <v>4.568145400000001</v>
       </c>
       <c r="N15">
-        <v>54.9581507</v>
+        <v>54.6318546</v>
       </c>
       <c r="O15">
-        <v>19.235352745</v>
+        <v>19.12114911</v>
       </c>
       <c r="P15">
-        <v>35.722797955</v>
+        <v>35.51070549000001</v>
       </c>
       <c r="Q15">
-        <v>53.722797955</v>
+        <v>53.51070549000001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2546337715364027</v>
+        <v>0.2562874067222258</v>
       </c>
       <c r="T15">
-        <v>1.026078044391471</v>
+        <v>1.034202969517916</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>13.95617708531041</v>
+        <v>12.95930729350252</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.2249844697811142</v>
+        <v>0.2243334583255581</v>
       </c>
       <c r="C16">
-        <v>597.3748753799775</v>
+        <v>593.2795490723753</v>
       </c>
       <c r="D16">
-        <v>655.8928753799776</v>
+        <v>658.2845490723754</v>
       </c>
       <c r="E16">
-        <v>-175.782</v>
+        <v>-169.295</v>
       </c>
       <c r="F16">
-        <v>90.81800000000001</v>
+        <v>97.30500000000002</v>
       </c>
       <c r="G16">
         <v>32.3</v>
@@ -2599,45 +2599,45 @@
         <v>59.2</v>
       </c>
       <c r="M16">
-        <v>4.568145400000001</v>
+        <v>5.040399000000001</v>
       </c>
       <c r="N16">
-        <v>54.6318546</v>
+        <v>54.159601</v>
       </c>
       <c r="O16">
-        <v>19.12114911</v>
+        <v>18.95586035</v>
       </c>
       <c r="P16">
-        <v>35.51070549000001</v>
+        <v>35.20374065</v>
       </c>
       <c r="Q16">
-        <v>53.51070549000001</v>
+        <v>53.20374065</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2562874067222258</v>
+        <v>0.2579799509712448</v>
       </c>
       <c r="T16">
-        <v>1.034202969517916</v>
+        <v>1.042519069353218</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.35</v>
       </c>
       <c r="W16">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>12.95930729350252</v>
+        <v>11.74510192546265</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.2243334583255581</v>
+        <v>0.2235459468700018</v>
       </c>
       <c r="C17">
-        <v>593.2795490723754</v>
+        <v>589.7091085356935</v>
       </c>
       <c r="D17">
-        <v>658.2845490723754</v>
+        <v>661.2011085356936</v>
       </c>
       <c r="E17">
-        <v>-169.295</v>
+        <v>-162.808</v>
       </c>
       <c r="F17">
-        <v>97.30500000000001</v>
+        <v>103.792</v>
       </c>
       <c r="G17">
         <v>32.3</v>
@@ -2681,28 +2681,28 @@
         <v>59.2</v>
       </c>
       <c r="M17">
-        <v>5.040399</v>
+        <v>5.376425600000001</v>
       </c>
       <c r="N17">
-        <v>54.159601</v>
+        <v>53.8235744</v>
       </c>
       <c r="O17">
-        <v>18.95586035</v>
+        <v>18.83825104</v>
       </c>
       <c r="P17">
-        <v>35.20374065</v>
+        <v>34.98532336</v>
       </c>
       <c r="Q17">
-        <v>53.20374065</v>
+        <v>52.98532336</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2579799509712448</v>
+        <v>0.2597127938928593</v>
       </c>
       <c r="T17">
-        <v>1.042519069353218</v>
+        <v>1.051033171565551</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.74510192546265</v>
+        <v>11.01103305512123</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.2235459468700018</v>
+        <v>0.2227584354144457</v>
       </c>
       <c r="C18">
-        <v>589.7091085356935</v>
+        <v>586.1646269083202</v>
       </c>
       <c r="D18">
-        <v>661.2011085356936</v>
+        <v>664.1436269083202</v>
       </c>
       <c r="E18">
-        <v>-162.808</v>
+        <v>-156.321</v>
       </c>
       <c r="F18">
-        <v>103.792</v>
+        <v>110.279</v>
       </c>
       <c r="G18">
         <v>32.3</v>
@@ -2763,28 +2763,28 @@
         <v>59.2</v>
       </c>
       <c r="M18">
-        <v>5.376425600000001</v>
+        <v>5.7124522</v>
       </c>
       <c r="N18">
-        <v>53.8235744</v>
+        <v>53.4875478</v>
       </c>
       <c r="O18">
-        <v>18.83825104</v>
+        <v>18.72064173</v>
       </c>
       <c r="P18">
-        <v>34.98532336</v>
+        <v>34.76690607</v>
       </c>
       <c r="Q18">
-        <v>52.98532336</v>
+        <v>52.76690607</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2597127938928593</v>
+        <v>0.2614873920655973</v>
       </c>
       <c r="T18">
-        <v>1.051033171565551</v>
+        <v>1.059752432867338</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.01103305512123</v>
+        <v>10.36332522834939</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.2227584354144457</v>
+        <v>0.2221698239588896</v>
       </c>
       <c r="C19">
-        <v>586.1646269083202</v>
+        <v>581.8941202865976</v>
       </c>
       <c r="D19">
-        <v>664.1436269083202</v>
+        <v>666.3601202865977</v>
       </c>
       <c r="E19">
-        <v>-156.321</v>
+        <v>-149.834</v>
       </c>
       <c r="F19">
-        <v>110.279</v>
+        <v>116.766</v>
       </c>
       <c r="G19">
         <v>32.3</v>
@@ -2845,45 +2845,45 @@
         <v>59.2</v>
       </c>
       <c r="M19">
-        <v>5.7124522</v>
+        <v>6.246981000000001</v>
       </c>
       <c r="N19">
-        <v>53.4875478</v>
+        <v>52.953019</v>
       </c>
       <c r="O19">
-        <v>18.72064173</v>
+        <v>18.53355665</v>
       </c>
       <c r="P19">
-        <v>34.76690607</v>
+        <v>34.41946235</v>
       </c>
       <c r="Q19">
-        <v>52.76690607</v>
+        <v>52.41946235</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2614873920655973</v>
+        <v>0.263305273120597</v>
       </c>
       <c r="T19">
-        <v>1.059752432867338</v>
+        <v>1.068684359078925</v>
       </c>
       <c r="U19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0.35</v>
       </c>
       <c r="W19">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>10.36332522834939</v>
+        <v>9.476577566027494</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.2221698239588896</v>
+        <v>0.2213933625033335</v>
       </c>
       <c r="C20">
-        <v>581.8941202865976</v>
+        <v>578.3537177066023</v>
       </c>
       <c r="D20">
-        <v>666.3601202865976</v>
+        <v>669.3067177066024</v>
       </c>
       <c r="E20">
-        <v>-149.834</v>
+        <v>-143.347</v>
       </c>
       <c r="F20">
-        <v>116.766</v>
+        <v>123.253</v>
       </c>
       <c r="G20">
         <v>32.3</v>
@@ -2927,28 +2927,28 @@
         <v>59.2</v>
       </c>
       <c r="M20">
-        <v>6.246981</v>
+        <v>6.5940355</v>
       </c>
       <c r="N20">
-        <v>52.953019</v>
+        <v>52.6059645</v>
       </c>
       <c r="O20">
-        <v>18.53355665</v>
+        <v>18.412087575</v>
       </c>
       <c r="P20">
-        <v>34.41946235</v>
+        <v>34.193876925</v>
       </c>
       <c r="Q20">
-        <v>52.41946235</v>
+        <v>52.193876925</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.263305273120597</v>
+        <v>0.2651680401275722</v>
       </c>
       <c r="T20">
-        <v>1.068684359078925</v>
+        <v>1.077836826678452</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.476577566027494</v>
+        <v>8.977810325710257</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.2213933625033335</v>
+        <v>0.2206169010477773</v>
       </c>
       <c r="C21">
-        <v>578.3537177066023</v>
+        <v>574.8394901624073</v>
       </c>
       <c r="D21">
-        <v>669.3067177066024</v>
+        <v>672.2794901624073</v>
       </c>
       <c r="E21">
-        <v>-143.347</v>
+        <v>-136.86</v>
       </c>
       <c r="F21">
-        <v>123.253</v>
+        <v>129.74</v>
       </c>
       <c r="G21">
         <v>32.3</v>
@@ -3009,28 +3009,28 @@
         <v>59.2</v>
       </c>
       <c r="M21">
-        <v>6.5940355</v>
+        <v>6.94109</v>
       </c>
       <c r="N21">
-        <v>52.6059645</v>
+        <v>52.25891</v>
       </c>
       <c r="O21">
-        <v>18.412087575</v>
+        <v>18.2906185</v>
       </c>
       <c r="P21">
-        <v>34.193876925</v>
+        <v>33.96829150000001</v>
       </c>
       <c r="Q21">
-        <v>52.193876925</v>
+        <v>51.96829150000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2651680401275722</v>
+        <v>0.2670773763097216</v>
       </c>
       <c r="T21">
-        <v>1.077836826678452</v>
+        <v>1.087218105967967</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.977810325710257</v>
+        <v>8.528919809424744</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.2206169010477773</v>
+        <v>0.2198404395922211</v>
       </c>
       <c r="C22">
-        <v>574.8394901624073</v>
+        <v>571.3517879847702</v>
       </c>
       <c r="D22">
-        <v>672.2794901624073</v>
+        <v>675.2787879847704</v>
       </c>
       <c r="E22">
-        <v>-136.86</v>
+        <v>-130.373</v>
       </c>
       <c r="F22">
-        <v>129.74</v>
+        <v>136.227</v>
       </c>
       <c r="G22">
         <v>32.3</v>
@@ -3091,28 +3091,28 @@
         <v>59.2</v>
       </c>
       <c r="M22">
-        <v>6.94109</v>
+        <v>7.288144500000001</v>
       </c>
       <c r="N22">
-        <v>52.25891</v>
+        <v>51.9118555</v>
       </c>
       <c r="O22">
-        <v>18.2906185</v>
+        <v>18.169149425</v>
       </c>
       <c r="P22">
-        <v>33.96829150000001</v>
+        <v>33.742706075</v>
       </c>
       <c r="Q22">
-        <v>51.96829150000001</v>
+        <v>51.742706075</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2670773763097216</v>
+        <v>0.2690350501167356</v>
       </c>
       <c r="T22">
-        <v>1.087218105967967</v>
+        <v>1.096836885998989</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.528919809424744</v>
+        <v>8.122780770880709</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.2198404395922211</v>
+        <v>0.219063978136665</v>
       </c>
       <c r="C23">
-        <v>571.3517879847703</v>
+        <v>567.8909677843087</v>
       </c>
       <c r="D23">
-        <v>675.2787879847704</v>
+        <v>678.3049677843087</v>
       </c>
       <c r="E23">
-        <v>-130.373</v>
+        <v>-123.886</v>
       </c>
       <c r="F23">
-        <v>136.227</v>
+        <v>142.714</v>
       </c>
       <c r="G23">
         <v>32.3</v>
@@ -3173,28 +3173,28 @@
         <v>59.2</v>
       </c>
       <c r="M23">
-        <v>7.2881445</v>
+        <v>7.635199</v>
       </c>
       <c r="N23">
-        <v>51.9118555</v>
+        <v>51.564801</v>
       </c>
       <c r="O23">
-        <v>18.169149425</v>
+        <v>18.04768035</v>
       </c>
       <c r="P23">
-        <v>33.742706075</v>
+        <v>33.51712065</v>
       </c>
       <c r="Q23">
-        <v>51.742706075</v>
+        <v>51.51712065</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2690350501167356</v>
+        <v>0.271042920688032</v>
       </c>
       <c r="T23">
-        <v>1.096836885998989</v>
+        <v>1.106702301415421</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.122780770880709</v>
+        <v>7.753563463113404</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.219063978136665</v>
+        <v>0.2184071166811088</v>
       </c>
       <c r="C24">
-        <v>567.8909677843087</v>
+        <v>563.9852772749998</v>
       </c>
       <c r="D24">
-        <v>678.3049677843087</v>
+        <v>680.8862772749999</v>
       </c>
       <c r="E24">
-        <v>-123.886</v>
+        <v>-117.399</v>
       </c>
       <c r="F24">
-        <v>142.714</v>
+        <v>149.201</v>
       </c>
       <c r="G24">
         <v>32.3</v>
@@ -3255,45 +3255,45 @@
         <v>59.2</v>
       </c>
       <c r="M24">
-        <v>7.635199</v>
+        <v>8.101614300000001</v>
       </c>
       <c r="N24">
-        <v>51.564801</v>
+        <v>51.0983857</v>
       </c>
       <c r="O24">
-        <v>18.04768035</v>
+        <v>17.884434995</v>
       </c>
       <c r="P24">
-        <v>33.51712065</v>
+        <v>33.213950705</v>
       </c>
       <c r="Q24">
-        <v>51.51712065</v>
+        <v>51.213950705</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.271042920688032</v>
+        <v>0.2731029437416997</v>
       </c>
       <c r="T24">
-        <v>1.106702301415421</v>
+        <v>1.116823961388125</v>
       </c>
       <c r="U24">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V24">
         <v>0.35</v>
       </c>
       <c r="W24">
-        <v>0.034775</v>
+        <v>0.035295</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y24">
-        <v>7.753563463113404</v>
+        <v>7.307185680266215</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.2184071166811088</v>
+        <v>0.2176358552255526</v>
       </c>
       <c r="C25">
-        <v>563.9852772749998</v>
+        <v>560.5543411016677</v>
       </c>
       <c r="D25">
-        <v>680.8862772749999</v>
+        <v>683.9423411016677</v>
       </c>
       <c r="E25">
-        <v>-117.399</v>
+        <v>-110.912</v>
       </c>
       <c r="F25">
-        <v>149.201</v>
+        <v>155.688</v>
       </c>
       <c r="G25">
         <v>32.3</v>
@@ -3337,28 +3337,28 @@
         <v>59.2</v>
       </c>
       <c r="M25">
-        <v>8.101614300000001</v>
+        <v>8.453858400000001</v>
       </c>
       <c r="N25">
-        <v>51.0983857</v>
+        <v>50.7461416</v>
       </c>
       <c r="O25">
-        <v>17.884434995</v>
+        <v>17.76114956</v>
       </c>
       <c r="P25">
-        <v>33.213950705</v>
+        <v>32.98499204</v>
       </c>
       <c r="Q25">
-        <v>51.213950705</v>
+        <v>50.98499204</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2731029437416997</v>
+        <v>0.2752171779283588</v>
       </c>
       <c r="T25">
-        <v>1.116823961388125</v>
+        <v>1.127211980833795</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.307185680266215</v>
+        <v>7.002719610255123</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.2176358552255526</v>
+        <v>0.2168645937699965</v>
       </c>
       <c r="C26">
-        <v>560.5543411016677</v>
+        <v>557.1509620537845</v>
       </c>
       <c r="D26">
-        <v>683.9423411016677</v>
+        <v>687.0259620537846</v>
       </c>
       <c r="E26">
-        <v>-110.912</v>
+        <v>-104.425</v>
       </c>
       <c r="F26">
-        <v>155.688</v>
+        <v>162.175</v>
       </c>
       <c r="G26">
         <v>32.3</v>
@@ -3419,28 +3419,28 @@
         <v>59.2</v>
       </c>
       <c r="M26">
-        <v>8.453858400000001</v>
+        <v>8.806102500000001</v>
       </c>
       <c r="N26">
-        <v>50.7461416</v>
+        <v>50.3938975</v>
       </c>
       <c r="O26">
-        <v>17.76114956</v>
+        <v>17.637864125</v>
       </c>
       <c r="P26">
-        <v>32.98499204</v>
+        <v>32.756033375</v>
       </c>
       <c r="Q26">
-        <v>50.98499204</v>
+        <v>50.756033375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2752171779283588</v>
+        <v>0.2773877916933287</v>
       </c>
       <c r="T26">
-        <v>1.127211980833795</v>
+        <v>1.137877014131349</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.002719610255123</v>
+        <v>6.722610825844917</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.2168645937699965</v>
+        <v>0.2160933323144404</v>
       </c>
       <c r="C27">
-        <v>557.1509620537845</v>
+        <v>553.7755145514482</v>
       </c>
       <c r="D27">
-        <v>687.0259620537846</v>
+        <v>690.1375145514482</v>
       </c>
       <c r="E27">
-        <v>-104.425</v>
+        <v>-97.93800000000002</v>
       </c>
       <c r="F27">
-        <v>162.175</v>
+        <v>168.662</v>
       </c>
       <c r="G27">
         <v>32.3</v>
@@ -3501,28 +3501,28 @@
         <v>59.2</v>
       </c>
       <c r="M27">
-        <v>8.806102500000001</v>
+        <v>9.1583466</v>
       </c>
       <c r="N27">
-        <v>50.3938975</v>
+        <v>50.0416534</v>
       </c>
       <c r="O27">
-        <v>17.637864125</v>
+        <v>17.51457869</v>
       </c>
       <c r="P27">
-        <v>32.756033375</v>
+        <v>32.52707471</v>
       </c>
       <c r="Q27">
-        <v>50.756033375</v>
+        <v>50.52707471</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2773877916933287</v>
+        <v>0.2796170706951897</v>
       </c>
       <c r="T27">
-        <v>1.137877014131349</v>
+        <v>1.14883029157208</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.722610825844917</v>
+        <v>6.46404887100473</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.2160933323144404</v>
+        <v>0.2153220708588842</v>
       </c>
       <c r="C28">
-        <v>553.7755145514482</v>
+        <v>550.4283798286367</v>
       </c>
       <c r="D28">
-        <v>690.1375145514482</v>
+        <v>693.2773798286368</v>
       </c>
       <c r="E28">
-        <v>-97.93800000000002</v>
+        <v>-91.45099999999999</v>
       </c>
       <c r="F28">
-        <v>168.662</v>
+        <v>175.149</v>
       </c>
       <c r="G28">
         <v>32.3</v>
@@ -3583,28 +3583,28 @@
         <v>59.2</v>
       </c>
       <c r="M28">
-        <v>9.1583466</v>
+        <v>9.510590700000002</v>
       </c>
       <c r="N28">
-        <v>50.0416534</v>
+        <v>49.6894093</v>
       </c>
       <c r="O28">
-        <v>17.51457869</v>
+        <v>17.391293255</v>
       </c>
       <c r="P28">
-        <v>32.52707471</v>
+        <v>32.298116045</v>
       </c>
       <c r="Q28">
-        <v>50.52707471</v>
+        <v>50.298116045</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2796170706951897</v>
+        <v>0.281907425834088</v>
       </c>
       <c r="T28">
-        <v>1.14883029157208</v>
+        <v>1.160083658805708</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.46404887100473</v>
+        <v>6.224639653560109</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.2153220708588842</v>
+        <v>0.2147328094033281</v>
       </c>
       <c r="C29">
-        <v>550.4283798286367</v>
+        <v>546.359629068585</v>
       </c>
       <c r="D29">
-        <v>693.2773798286368</v>
+        <v>695.6956290685852</v>
       </c>
       <c r="E29">
-        <v>-91.45099999999999</v>
+        <v>-84.964</v>
       </c>
       <c r="F29">
-        <v>175.149</v>
+        <v>181.636</v>
       </c>
       <c r="G29">
         <v>32.3</v>
@@ -3665,45 +3665,45 @@
         <v>59.2</v>
       </c>
       <c r="M29">
-        <v>9.510590700000002</v>
+        <v>10.0444708</v>
       </c>
       <c r="N29">
-        <v>49.6894093</v>
+        <v>49.1555292</v>
       </c>
       <c r="O29">
-        <v>17.391293255</v>
+        <v>17.20443522</v>
       </c>
       <c r="P29">
-        <v>32.298116045</v>
+        <v>31.95109398</v>
       </c>
       <c r="Q29">
-        <v>50.298116045</v>
+        <v>49.95109398</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.281907425834088</v>
+        <v>0.2842614019490668</v>
       </c>
       <c r="T29">
-        <v>1.160083658805708</v>
+        <v>1.171649619573603</v>
       </c>
       <c r="U29">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V29">
         <v>0.35</v>
       </c>
       <c r="W29">
-        <v>0.035295</v>
+        <v>0.035945</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>6.224639653560109</v>
+        <v>5.893789845055849</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.2147328094033281</v>
+        <v>0.2139680479477719</v>
       </c>
       <c r="C30">
-        <v>546.359629068585</v>
+        <v>543.0363763345091</v>
       </c>
       <c r="D30">
-        <v>695.6956290685852</v>
+        <v>698.8593763345092</v>
       </c>
       <c r="E30">
-        <v>-84.964</v>
+        <v>-78.47699999999998</v>
       </c>
       <c r="F30">
-        <v>181.636</v>
+        <v>188.123</v>
       </c>
       <c r="G30">
         <v>32.3</v>
@@ -3747,28 +3747,28 @@
         <v>59.2</v>
       </c>
       <c r="M30">
-        <v>10.0444708</v>
+        <v>10.4032019</v>
       </c>
       <c r="N30">
-        <v>49.1555292</v>
+        <v>48.7967981</v>
       </c>
       <c r="O30">
-        <v>17.20443522</v>
+        <v>17.078879335</v>
       </c>
       <c r="P30">
-        <v>31.95109398</v>
+        <v>31.717918765</v>
       </c>
       <c r="Q30">
-        <v>49.95109398</v>
+        <v>49.71791876500001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2842614019490668</v>
+        <v>0.286681687250383</v>
       </c>
       <c r="T30">
-        <v>1.171649619573603</v>
+        <v>1.183541382053271</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.893789845055849</v>
+        <v>5.690555712467716</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.2139680479477719</v>
+        <v>0.2132032864922157</v>
       </c>
       <c r="C31">
-        <v>543.0363763345092</v>
+        <v>539.7420299859027</v>
       </c>
       <c r="D31">
-        <v>698.8593763345092</v>
+        <v>702.0520299859028</v>
       </c>
       <c r="E31">
-        <v>-78.47700000000003</v>
+        <v>-71.99000000000001</v>
       </c>
       <c r="F31">
-        <v>188.123</v>
+        <v>194.61</v>
       </c>
       <c r="G31">
         <v>32.3</v>
@@ -3829,28 +3829,28 @@
         <v>59.2</v>
       </c>
       <c r="M31">
-        <v>10.4032019</v>
+        <v>10.761933</v>
       </c>
       <c r="N31">
-        <v>48.7967981</v>
+        <v>48.438067</v>
       </c>
       <c r="O31">
-        <v>17.078879335</v>
+        <v>16.95332345</v>
       </c>
       <c r="P31">
-        <v>31.717918765</v>
+        <v>31.48474355</v>
       </c>
       <c r="Q31">
-        <v>49.71791876500001</v>
+        <v>49.48474355</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.286681687250383</v>
+        <v>0.2891711235603082</v>
       </c>
       <c r="T31">
-        <v>1.183541382053271</v>
+        <v>1.195772909175214</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.690555712467717</v>
+        <v>5.500870522052126</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.2132032864922157</v>
+        <v>0.2124385250366596</v>
       </c>
       <c r="C32">
-        <v>539.7420299859027</v>
+        <v>536.4769880067747</v>
       </c>
       <c r="D32">
-        <v>702.0520299859028</v>
+        <v>705.2739880067747</v>
       </c>
       <c r="E32">
-        <v>-71.99000000000001</v>
+        <v>-65.50300000000001</v>
       </c>
       <c r="F32">
-        <v>194.61</v>
+        <v>201.097</v>
       </c>
       <c r="G32">
         <v>32.3</v>
@@ -3911,28 +3911,28 @@
         <v>59.2</v>
       </c>
       <c r="M32">
-        <v>10.761933</v>
+        <v>11.1206641</v>
       </c>
       <c r="N32">
-        <v>48.438067</v>
+        <v>48.0793359</v>
       </c>
       <c r="O32">
-        <v>16.95332345</v>
+        <v>16.827767565</v>
       </c>
       <c r="P32">
-        <v>31.48474355</v>
+        <v>31.25156833500001</v>
       </c>
       <c r="Q32">
-        <v>49.48474355</v>
+        <v>49.251568335</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2891711235603082</v>
+        <v>0.2917327174444342</v>
       </c>
       <c r="T32">
-        <v>1.195772909175214</v>
+        <v>1.208358973315184</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.500870522052126</v>
+        <v>5.323423085856896</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.2124385250366596</v>
+        <v>0.2116737635811035</v>
       </c>
       <c r="C33">
-        <v>536.4769880067747</v>
+        <v>533.2416557207603</v>
       </c>
       <c r="D33">
-        <v>705.2739880067747</v>
+        <v>708.5256557207604</v>
       </c>
       <c r="E33">
-        <v>-65.50300000000001</v>
+        <v>-59.01599999999999</v>
       </c>
       <c r="F33">
-        <v>201.097</v>
+        <v>207.584</v>
       </c>
       <c r="G33">
         <v>32.3</v>
@@ -3993,28 +3993,28 @@
         <v>59.2</v>
       </c>
       <c r="M33">
-        <v>11.1206641</v>
+        <v>11.4793952</v>
       </c>
       <c r="N33">
-        <v>48.0793359</v>
+        <v>47.7206048</v>
       </c>
       <c r="O33">
-        <v>16.827767565</v>
+        <v>16.70221168</v>
       </c>
       <c r="P33">
-        <v>31.25156833500001</v>
+        <v>31.01839312</v>
       </c>
       <c r="Q33">
-        <v>49.251568335</v>
+        <v>49.01839312</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2917327174444342</v>
+        <v>0.2943696523251522</v>
       </c>
       <c r="T33">
-        <v>1.208358973315184</v>
+        <v>1.221315215812213</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.323423085856896</v>
+        <v>5.157066114423867</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.2116737635811035</v>
+        <v>0.2109090021255473</v>
       </c>
       <c r="C34">
-        <v>533.2416557207603</v>
+        <v>530.0364459611003</v>
       </c>
       <c r="D34">
-        <v>708.5256557207604</v>
+        <v>711.8074459611004</v>
       </c>
       <c r="E34">
-        <v>-59.01599999999999</v>
+        <v>-52.529</v>
       </c>
       <c r="F34">
-        <v>207.584</v>
+        <v>214.071</v>
       </c>
       <c r="G34">
         <v>32.3</v>
@@ -4075,28 +4075,28 @@
         <v>59.2</v>
       </c>
       <c r="M34">
-        <v>11.4793952</v>
+        <v>11.8381263</v>
       </c>
       <c r="N34">
-        <v>47.7206048</v>
+        <v>47.3618737</v>
       </c>
       <c r="O34">
-        <v>16.70221168</v>
+        <v>16.576655795</v>
       </c>
       <c r="P34">
-        <v>31.01839312</v>
+        <v>30.785217905</v>
       </c>
       <c r="Q34">
-        <v>49.01839312</v>
+        <v>48.785217905</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2943696523251522</v>
+        <v>0.2970853016799214</v>
       </c>
       <c r="T34">
-        <v>1.221315215812213</v>
+        <v>1.234658211816616</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.157066114423867</v>
+        <v>5.00079138368375</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.2109090021255473</v>
+        <v>0.2101442406699911</v>
       </c>
       <c r="C35">
-        <v>530.0364459611003</v>
+        <v>526.8617792453682</v>
       </c>
       <c r="D35">
-        <v>711.8074459611004</v>
+        <v>715.1197792453682</v>
       </c>
       <c r="E35">
-        <v>-52.529</v>
+        <v>-46.042</v>
       </c>
       <c r="F35">
-        <v>214.071</v>
+        <v>220.558</v>
       </c>
       <c r="G35">
         <v>32.3</v>
@@ -4157,28 +4157,28 @@
         <v>59.2</v>
       </c>
       <c r="M35">
-        <v>11.8381263</v>
+        <v>12.1968574</v>
       </c>
       <c r="N35">
-        <v>47.3618737</v>
+        <v>47.0031426</v>
       </c>
       <c r="O35">
-        <v>16.576655795</v>
+        <v>16.45109991</v>
       </c>
       <c r="P35">
-        <v>30.785217905</v>
+        <v>30.55204269</v>
       </c>
       <c r="Q35">
-        <v>48.785217905</v>
+        <v>48.55204269000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2970853016799214</v>
+        <v>0.2998832434393806</v>
       </c>
       <c r="T35">
-        <v>1.234658211816616</v>
+        <v>1.248405541033273</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.00079138368375</v>
+        <v>4.85370928416364</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.2101442406699911</v>
+        <v>0.209379479214435</v>
       </c>
       <c r="C36">
-        <v>526.8617792453682</v>
+        <v>523.7180839550972</v>
       </c>
       <c r="D36">
-        <v>715.1197792453682</v>
+        <v>718.4630839550973</v>
       </c>
       <c r="E36">
-        <v>-46.042</v>
+        <v>-39.55499999999998</v>
       </c>
       <c r="F36">
-        <v>220.558</v>
+        <v>227.045</v>
       </c>
       <c r="G36">
         <v>32.3</v>
@@ -4239,28 +4239,28 @@
         <v>59.2</v>
       </c>
       <c r="M36">
-        <v>12.1968574</v>
+        <v>12.5555885</v>
       </c>
       <c r="N36">
-        <v>47.0031426</v>
+        <v>46.6444115</v>
       </c>
       <c r="O36">
-        <v>16.45109991</v>
+        <v>16.325544025</v>
       </c>
       <c r="P36">
-        <v>30.55204269</v>
+        <v>30.318867475</v>
       </c>
       <c r="Q36">
-        <v>48.55204269000001</v>
+        <v>48.318867475</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2998832434393806</v>
+        <v>0.3027672757145154</v>
       </c>
       <c r="T36">
-        <v>1.248405541033273</v>
+        <v>1.262575864995058</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.85370928416364</v>
+        <v>4.715031876044678</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.209379479214435</v>
+        <v>0.2086147177588789</v>
       </c>
       <c r="C37">
-        <v>523.7180839550972</v>
+        <v>520.605796520472</v>
       </c>
       <c r="D37">
-        <v>718.4630839550973</v>
+        <v>721.8377965204721</v>
       </c>
       <c r="E37">
-        <v>-39.55499999999998</v>
+        <v>-33.06799999999998</v>
       </c>
       <c r="F37">
-        <v>227.045</v>
+        <v>233.532</v>
       </c>
       <c r="G37">
         <v>32.3</v>
@@ -4321,28 +4321,28 @@
         <v>59.2</v>
       </c>
       <c r="M37">
-        <v>12.5555885</v>
+        <v>12.9143196</v>
       </c>
       <c r="N37">
-        <v>46.6444115</v>
+        <v>46.2856804</v>
       </c>
       <c r="O37">
-        <v>16.325544025</v>
+        <v>16.19998814</v>
       </c>
       <c r="P37">
-        <v>30.318867475</v>
+        <v>30.08569226</v>
       </c>
       <c r="Q37">
-        <v>48.318867475</v>
+        <v>48.08569226</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.3027672757145154</v>
+        <v>0.3057414339982483</v>
       </c>
       <c r="T37">
-        <v>1.262575864995058</v>
+        <v>1.277189011580649</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.715031876044678</v>
+        <v>4.584058768376771</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.2086147177588789</v>
+        <v>0.2084512063033227</v>
       </c>
       <c r="C38">
-        <v>520.6057965204719</v>
+        <v>514.8444520595058</v>
       </c>
       <c r="D38">
-        <v>721.837796520472</v>
+        <v>722.5634520595058</v>
       </c>
       <c r="E38">
-        <v>-33.06800000000001</v>
+        <v>-26.58100000000002</v>
       </c>
       <c r="F38">
-        <v>233.532</v>
+        <v>240.019</v>
       </c>
       <c r="G38">
         <v>32.3</v>
@@ -4403,45 +4403,45 @@
         <v>59.2</v>
       </c>
       <c r="M38">
-        <v>12.9143196</v>
+        <v>13.8730982</v>
       </c>
       <c r="N38">
-        <v>46.2856804</v>
+        <v>45.3269018</v>
       </c>
       <c r="O38">
-        <v>16.19998814</v>
+        <v>15.86441563</v>
       </c>
       <c r="P38">
-        <v>30.08569226</v>
+        <v>29.46248617</v>
       </c>
       <c r="Q38">
-        <v>48.08569226</v>
+        <v>47.46248617000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.3057414339982483</v>
+        <v>0.3088100100052742</v>
       </c>
       <c r="T38">
-        <v>1.277189011580649</v>
+        <v>1.292266067581656</v>
       </c>
       <c r="U38">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V38">
         <v>0.35</v>
       </c>
       <c r="W38">
-        <v>0.035945</v>
+        <v>0.03757000000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>4.584058768376772</v>
+        <v>4.267251564614456</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.2084512063033227</v>
+        <v>0.2077026948477666</v>
       </c>
       <c r="C39">
-        <v>514.8444520595058</v>
+        <v>511.6980204283107</v>
       </c>
       <c r="D39">
-        <v>722.5634520595058</v>
+        <v>725.9040204283108</v>
       </c>
       <c r="E39">
-        <v>-26.58100000000002</v>
+        <v>-20.09399999999999</v>
       </c>
       <c r="F39">
-        <v>240.019</v>
+        <v>246.506</v>
       </c>
       <c r="G39">
         <v>32.3</v>
@@ -4485,28 +4485,28 @@
         <v>59.2</v>
       </c>
       <c r="M39">
-        <v>13.8730982</v>
+        <v>14.2480468</v>
       </c>
       <c r="N39">
-        <v>45.3269018</v>
+        <v>44.9519532</v>
       </c>
       <c r="O39">
-        <v>15.86441563</v>
+        <v>15.73318362</v>
       </c>
       <c r="P39">
-        <v>29.46248617</v>
+        <v>29.21876958</v>
       </c>
       <c r="Q39">
-        <v>47.46248617000001</v>
+        <v>47.21876958</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.3088100100052742</v>
+        <v>0.3119775723351074</v>
       </c>
       <c r="T39">
-        <v>1.292266067581656</v>
+        <v>1.307829480227856</v>
       </c>
       <c r="U39">
         <v>0.0578</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.267251564614456</v>
+        <v>4.154955470808812</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2077026948477666</v>
+        <v>0.2069541833922104</v>
       </c>
       <c r="C40">
-        <v>511.6980204283107</v>
+        <v>508.5826206157068</v>
       </c>
       <c r="D40">
-        <v>725.9040204283108</v>
+        <v>729.2756206157069</v>
       </c>
       <c r="E40">
-        <v>-20.09399999999999</v>
+        <v>-13.607</v>
       </c>
       <c r="F40">
-        <v>246.506</v>
+        <v>252.993</v>
       </c>
       <c r="G40">
         <v>32.3</v>
@@ -4567,28 +4567,28 @@
         <v>59.2</v>
       </c>
       <c r="M40">
-        <v>14.2480468</v>
+        <v>14.6229954</v>
       </c>
       <c r="N40">
-        <v>44.9519532</v>
+        <v>44.5770046</v>
       </c>
       <c r="O40">
-        <v>15.73318362</v>
+        <v>15.60195161</v>
       </c>
       <c r="P40">
-        <v>29.21876958</v>
+        <v>28.97505299</v>
       </c>
       <c r="Q40">
-        <v>47.21876958</v>
+        <v>46.97505299</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.3119775723351074</v>
+        <v>0.3152489891675581</v>
       </c>
       <c r="T40">
-        <v>1.307829480227856</v>
+        <v>1.323903168698522</v>
       </c>
       <c r="U40">
         <v>0.0578</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.154955470808812</v>
+        <v>4.048418151044483</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2069541833922104</v>
+        <v>0.2071156719366543</v>
       </c>
       <c r="C41">
-        <v>508.5826206157068</v>
+        <v>501.3655634733491</v>
       </c>
       <c r="D41">
-        <v>729.2756206157069</v>
+        <v>728.5455634733491</v>
       </c>
       <c r="E41">
-        <v>-13.607</v>
+        <v>-7.120000000000005</v>
       </c>
       <c r="F41">
-        <v>252.993</v>
+        <v>259.48</v>
       </c>
       <c r="G41">
         <v>32.3</v>
@@ -4649,45 +4649,45 @@
         <v>59.2</v>
       </c>
       <c r="M41">
-        <v>14.6229954</v>
+        <v>15.906124</v>
       </c>
       <c r="N41">
-        <v>44.5770046</v>
+        <v>43.293876</v>
       </c>
       <c r="O41">
-        <v>15.60195161</v>
+        <v>15.1528566</v>
       </c>
       <c r="P41">
-        <v>28.97505299</v>
+        <v>28.1410194</v>
       </c>
       <c r="Q41">
-        <v>46.97505299</v>
+        <v>46.1410194</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.3152489891675581</v>
+        <v>0.3186294532277572</v>
       </c>
       <c r="T41">
-        <v>1.323903168698522</v>
+        <v>1.340512646784877</v>
       </c>
       <c r="U41">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V41">
         <v>0.35</v>
       </c>
       <c r="W41">
-        <v>0.03757000000000001</v>
+        <v>0.039845</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>4.048418151044483</v>
+        <v>3.721836947832168</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2071156719366543</v>
+        <v>0.2063899104810981</v>
       </c>
       <c r="C42">
-        <v>501.3655634733491</v>
+        <v>498.1711133415279</v>
       </c>
       <c r="D42">
-        <v>728.5455634733491</v>
+        <v>731.838113341528</v>
       </c>
       <c r="E42">
-        <v>-7.120000000000005</v>
+        <v>-0.6329999999999814</v>
       </c>
       <c r="F42">
-        <v>259.48</v>
+        <v>265.967</v>
       </c>
       <c r="G42">
         <v>32.3</v>
@@ -4731,28 +4731,28 @@
         <v>59.2</v>
       </c>
       <c r="M42">
-        <v>15.906124</v>
+        <v>16.3037771</v>
       </c>
       <c r="N42">
-        <v>43.293876</v>
+        <v>42.8962229</v>
       </c>
       <c r="O42">
-        <v>15.1528566</v>
+        <v>15.013678015</v>
       </c>
       <c r="P42">
-        <v>28.1410194</v>
+        <v>27.882544885</v>
       </c>
       <c r="Q42">
-        <v>46.1410194</v>
+        <v>45.882544885</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.3186294532277572</v>
+        <v>0.3221245092899968</v>
       </c>
       <c r="T42">
-        <v>1.340512646784877</v>
+        <v>1.357685158026701</v>
       </c>
       <c r="U42">
         <v>0.0613</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.721836947832168</v>
+        <v>3.631060436909432</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2063899104810981</v>
+        <v>0.2056641490255419</v>
       </c>
       <c r="C43">
-        <v>498.1711133415279</v>
+        <v>495.0065586653094</v>
       </c>
       <c r="D43">
-        <v>731.838113341528</v>
+        <v>735.1605586653095</v>
       </c>
       <c r="E43">
-        <v>-0.6329999999999814</v>
+        <v>5.854000000000042</v>
       </c>
       <c r="F43">
-        <v>265.967</v>
+        <v>272.4540000000001</v>
       </c>
       <c r="G43">
         <v>32.3</v>
@@ -4813,28 +4813,28 @@
         <v>59.2</v>
       </c>
       <c r="M43">
-        <v>16.3037771</v>
+        <v>16.7014302</v>
       </c>
       <c r="N43">
-        <v>42.8962229</v>
+        <v>42.4985698</v>
       </c>
       <c r="O43">
-        <v>15.013678015</v>
+        <v>14.87449943</v>
       </c>
       <c r="P43">
-        <v>27.882544885</v>
+        <v>27.62407037</v>
       </c>
       <c r="Q43">
-        <v>45.882544885</v>
+        <v>45.62407037</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.3221245092899968</v>
+        <v>0.3257400845267965</v>
       </c>
       <c r="T43">
-        <v>1.357685158026701</v>
+        <v>1.375449824828588</v>
       </c>
       <c r="U43">
         <v>0.0613</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.631060436909432</v>
+        <v>3.544606616983017</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.205664149025542</v>
+        <v>0.2057209875699859</v>
       </c>
       <c r="C44">
-        <v>495.0065586653093</v>
+        <v>488.2582705334511</v>
       </c>
       <c r="D44">
-        <v>735.1605586653094</v>
+        <v>734.8992705334512</v>
       </c>
       <c r="E44">
-        <v>5.853999999999985</v>
+        <v>12.34100000000001</v>
       </c>
       <c r="F44">
-        <v>272.454</v>
+        <v>278.941</v>
       </c>
       <c r="G44">
         <v>32.3</v>
@@ -4895,45 +4895,45 @@
         <v>59.2</v>
       </c>
       <c r="M44">
-        <v>16.7014302</v>
+        <v>17.8801181</v>
       </c>
       <c r="N44">
-        <v>42.4985698</v>
+        <v>41.3198819</v>
       </c>
       <c r="O44">
-        <v>14.87449943</v>
+        <v>14.461958665</v>
       </c>
       <c r="P44">
-        <v>27.62407037</v>
+        <v>26.857923235</v>
       </c>
       <c r="Q44">
-        <v>45.62407037</v>
+        <v>44.857923235</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.3257400845267965</v>
+        <v>0.3294825220526067</v>
       </c>
       <c r="T44">
-        <v>1.375449824828588</v>
+        <v>1.393837813272647</v>
       </c>
       <c r="U44">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V44">
         <v>0.35</v>
       </c>
       <c r="W44">
-        <v>0.039845</v>
+        <v>0.04166500000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>3.544606616983017</v>
+        <v>3.310940099439275</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2057209875699859</v>
+        <v>0.2050134261144297</v>
       </c>
       <c r="C45">
-        <v>488.2582705334511</v>
+        <v>485.037241313906</v>
       </c>
       <c r="D45">
-        <v>734.8992705334512</v>
+        <v>738.165241313906</v>
       </c>
       <c r="E45">
-        <v>12.34100000000001</v>
+        <v>18.82799999999997</v>
       </c>
       <c r="F45">
-        <v>278.941</v>
+        <v>285.428</v>
       </c>
       <c r="G45">
         <v>32.3</v>
@@ -4977,28 +4977,28 @@
         <v>59.2</v>
       </c>
       <c r="M45">
-        <v>17.8801181</v>
+        <v>18.2959348</v>
       </c>
       <c r="N45">
-        <v>41.3198819</v>
+        <v>40.90406520000001</v>
       </c>
       <c r="O45">
-        <v>14.461958665</v>
+        <v>14.31642282</v>
       </c>
       <c r="P45">
-        <v>26.857923235</v>
+        <v>26.58764238000001</v>
       </c>
       <c r="Q45">
-        <v>44.857923235</v>
+        <v>44.58764238000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.3294825220526067</v>
+        <v>0.3333586180614815</v>
       </c>
       <c r="T45">
-        <v>1.393837813272647</v>
+        <v>1.412882515589708</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.310940099439275</v>
+        <v>3.235691460815656</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2050134261144297</v>
+        <v>0.2043058646588735</v>
       </c>
       <c r="C46">
-        <v>485.037241313906</v>
+        <v>481.8453703219655</v>
       </c>
       <c r="D46">
-        <v>738.165241313906</v>
+        <v>741.4603703219656</v>
       </c>
       <c r="E46">
-        <v>18.82799999999997</v>
+        <v>25.315</v>
       </c>
       <c r="F46">
-        <v>285.428</v>
+        <v>291.915</v>
       </c>
       <c r="G46">
         <v>32.3</v>
@@ -5059,28 +5059,28 @@
         <v>59.2</v>
       </c>
       <c r="M46">
-        <v>18.2959348</v>
+        <v>18.7117515</v>
       </c>
       <c r="N46">
-        <v>40.90406520000001</v>
+        <v>40.4882485</v>
       </c>
       <c r="O46">
-        <v>14.31642282</v>
+        <v>14.170886975</v>
       </c>
       <c r="P46">
-        <v>26.58764238000001</v>
+        <v>26.317361525</v>
       </c>
       <c r="Q46">
-        <v>44.58764238000001</v>
+        <v>44.317361525</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.3333586180614815</v>
+        <v>0.3373756630161336</v>
       </c>
       <c r="T46">
-        <v>1.412882515589708</v>
+        <v>1.43261975253648</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.235691460815656</v>
+        <v>3.163787206130864</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2043058646588735</v>
+        <v>0.2035983032033174</v>
       </c>
       <c r="C47">
-        <v>481.8453703219655</v>
+        <v>478.6830497907063</v>
       </c>
       <c r="D47">
-        <v>741.4603703219656</v>
+        <v>744.7850497907064</v>
       </c>
       <c r="E47">
-        <v>25.315</v>
+        <v>31.80200000000002</v>
       </c>
       <c r="F47">
-        <v>291.915</v>
+        <v>298.402</v>
       </c>
       <c r="G47">
         <v>32.3</v>
@@ -5141,28 +5141,28 @@
         <v>59.2</v>
       </c>
       <c r="M47">
-        <v>18.7117515</v>
+        <v>19.1275682</v>
       </c>
       <c r="N47">
-        <v>40.4882485</v>
+        <v>40.0724318</v>
       </c>
       <c r="O47">
-        <v>14.170886975</v>
+        <v>14.02535113</v>
       </c>
       <c r="P47">
-        <v>26.317361525</v>
+        <v>26.04708067</v>
       </c>
       <c r="Q47">
-        <v>44.317361525</v>
+        <v>44.04708067</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.3373756630161336</v>
+        <v>0.3415414874135507</v>
       </c>
       <c r="T47">
-        <v>1.43261975253648</v>
+        <v>1.453087998259059</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.163787206130864</v>
+        <v>3.095009223388888</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2035983032033174</v>
+        <v>0.2028907417477612</v>
       </c>
       <c r="C48">
-        <v>478.6830497907063</v>
+        <v>475.5506790199232</v>
       </c>
       <c r="D48">
-        <v>744.7850497907064</v>
+        <v>748.1396790199233</v>
       </c>
       <c r="E48">
-        <v>31.80200000000002</v>
+        <v>38.28900000000004</v>
       </c>
       <c r="F48">
-        <v>298.402</v>
+        <v>304.8890000000001</v>
       </c>
       <c r="G48">
         <v>32.3</v>
@@ -5223,28 +5223,28 @@
         <v>59.2</v>
       </c>
       <c r="M48">
-        <v>19.1275682</v>
+        <v>19.54338490000001</v>
       </c>
       <c r="N48">
-        <v>40.0724318</v>
+        <v>39.6566151</v>
       </c>
       <c r="O48">
-        <v>14.02535113</v>
+        <v>13.879815285</v>
       </c>
       <c r="P48">
-        <v>26.04708067</v>
+        <v>25.776799815</v>
       </c>
       <c r="Q48">
-        <v>44.04708067</v>
+        <v>43.776799815</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.3415414874135507</v>
+        <v>0.3458645127316249</v>
       </c>
       <c r="T48">
-        <v>1.453087998259059</v>
+        <v>1.474328630612678</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.095009223388888</v>
+        <v>3.029157963316784</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2028907417477612</v>
+        <v>0.2046167802922051</v>
       </c>
       <c r="C49">
-        <v>475.5506790199232</v>
+        <v>460.9328132496918</v>
       </c>
       <c r="D49">
-        <v>748.1396790199233</v>
+        <v>740.0088132496919</v>
       </c>
       <c r="E49">
-        <v>38.28900000000004</v>
+        <v>44.77600000000001</v>
       </c>
       <c r="F49">
-        <v>304.8890000000001</v>
+        <v>311.376</v>
       </c>
       <c r="G49">
         <v>32.3</v>
@@ -5305,45 +5305,45 @@
         <v>59.2</v>
       </c>
       <c r="M49">
-        <v>19.54338490000001</v>
+        <v>22.3879344</v>
       </c>
       <c r="N49">
-        <v>39.6566151</v>
+        <v>36.8120656</v>
       </c>
       <c r="O49">
-        <v>13.879815285</v>
+        <v>12.88422296</v>
       </c>
       <c r="P49">
-        <v>25.776799815</v>
+        <v>23.92784264</v>
       </c>
       <c r="Q49">
-        <v>43.776799815</v>
+        <v>41.92784263999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.3458645127316249</v>
+        <v>0.3503538082542405</v>
       </c>
       <c r="T49">
-        <v>1.474328630612678</v>
+        <v>1.496386210364514</v>
       </c>
       <c r="U49">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V49">
         <v>0.35</v>
       </c>
       <c r="W49">
-        <v>0.04166500000000001</v>
+        <v>0.04673500000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>3.029157963316784</v>
+        <v>2.644281466181176</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2046167802922051</v>
+        <v>0.2039599188366489</v>
       </c>
       <c r="C50">
-        <v>460.9328132496918</v>
+        <v>457.5191789277407</v>
       </c>
       <c r="D50">
-        <v>740.0088132496919</v>
+        <v>743.0821789277408</v>
       </c>
       <c r="E50">
-        <v>44.77600000000001</v>
+        <v>51.26299999999998</v>
       </c>
       <c r="F50">
-        <v>311.376</v>
+        <v>317.863</v>
       </c>
       <c r="G50">
         <v>32.3</v>
@@ -5387,28 +5387,28 @@
         <v>59.2</v>
       </c>
       <c r="M50">
-        <v>22.3879344</v>
+        <v>22.8543497</v>
       </c>
       <c r="N50">
-        <v>36.8120656</v>
+        <v>36.3456503</v>
       </c>
       <c r="O50">
-        <v>12.88422296</v>
+        <v>12.720977605</v>
       </c>
       <c r="P50">
-        <v>23.92784264</v>
+        <v>23.624672695</v>
       </c>
       <c r="Q50">
-        <v>41.92784263999999</v>
+        <v>41.624672695</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.3503538082542405</v>
+        <v>0.3550191545816646</v>
       </c>
       <c r="T50">
-        <v>1.496386210364514</v>
+        <v>1.519308793243872</v>
       </c>
       <c r="U50">
         <v>0.07190000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.644281466181176</v>
+        <v>2.590316538299928</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2039599188366489</v>
+        <v>0.2033030573810927</v>
       </c>
       <c r="C51">
-        <v>457.5191789277407</v>
+        <v>454.131179352014</v>
       </c>
       <c r="D51">
-        <v>743.0821789277408</v>
+        <v>746.1811793520141</v>
       </c>
       <c r="E51">
-        <v>51.26299999999998</v>
+        <v>57.75</v>
       </c>
       <c r="F51">
-        <v>317.863</v>
+        <v>324.35</v>
       </c>
       <c r="G51">
         <v>32.3</v>
@@ -5469,28 +5469,28 @@
         <v>59.2</v>
       </c>
       <c r="M51">
-        <v>22.8543497</v>
+        <v>23.32076500000001</v>
       </c>
       <c r="N51">
-        <v>36.3456503</v>
+        <v>35.87923499999999</v>
       </c>
       <c r="O51">
-        <v>12.720977605</v>
+        <v>12.55773225</v>
       </c>
       <c r="P51">
-        <v>23.624672695</v>
+        <v>23.32150275</v>
       </c>
       <c r="Q51">
-        <v>41.624672695</v>
+        <v>41.32150274999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.3550191545816646</v>
+        <v>0.3598711147621855</v>
       </c>
       <c r="T51">
-        <v>1.519308793243872</v>
+        <v>1.543148279438404</v>
       </c>
       <c r="U51">
         <v>0.07190000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.590316538299928</v>
+        <v>2.538510207533929</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2033030573810927</v>
+        <v>0.2039390459255366</v>
       </c>
       <c r="C52">
-        <v>454.131179352014</v>
+        <v>444.6432589950583</v>
       </c>
       <c r="D52">
-        <v>746.1811793520141</v>
+        <v>743.1802589950584</v>
       </c>
       <c r="E52">
-        <v>57.75</v>
+        <v>64.23700000000002</v>
       </c>
       <c r="F52">
-        <v>324.35</v>
+        <v>330.837</v>
       </c>
       <c r="G52">
         <v>32.3</v>
@@ -5551,45 +5551,45 @@
         <v>59.2</v>
       </c>
       <c r="M52">
-        <v>23.32076500000001</v>
+        <v>25.07744460000001</v>
       </c>
       <c r="N52">
-        <v>35.87923499999999</v>
+        <v>34.1225554</v>
       </c>
       <c r="O52">
-        <v>12.55773225</v>
+        <v>11.94289439</v>
       </c>
       <c r="P52">
-        <v>23.32150275</v>
+        <v>22.17966101</v>
       </c>
       <c r="Q52">
-        <v>41.32150274999999</v>
+        <v>40.17966101</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.3598711147621855</v>
+        <v>0.3649211141337482</v>
       </c>
       <c r="T52">
-        <v>1.543148279438404</v>
+        <v>1.567960805885775</v>
       </c>
       <c r="U52">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V52">
         <v>0.35</v>
       </c>
       <c r="W52">
-        <v>0.04673500000000001</v>
+        <v>0.04927000000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.538510207533929</v>
+        <v>2.360687101268683</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2039390459255366</v>
+        <v>0.2033075344699805</v>
       </c>
       <c r="C53">
-        <v>444.6432589950583</v>
+        <v>441.1359694494047</v>
       </c>
       <c r="D53">
-        <v>743.1802589950584</v>
+        <v>746.1599694494048</v>
       </c>
       <c r="E53">
-        <v>64.23700000000002</v>
+        <v>70.72399999999999</v>
       </c>
       <c r="F53">
-        <v>330.837</v>
+        <v>337.324</v>
       </c>
       <c r="G53">
         <v>32.3</v>
@@ -5633,28 +5633,28 @@
         <v>59.2</v>
       </c>
       <c r="M53">
-        <v>25.07744460000001</v>
+        <v>25.5691592</v>
       </c>
       <c r="N53">
-        <v>34.1225554</v>
+        <v>33.6308408</v>
       </c>
       <c r="O53">
-        <v>11.94289439</v>
+        <v>11.77079428</v>
       </c>
       <c r="P53">
-        <v>22.17966101</v>
+        <v>21.86004652</v>
       </c>
       <c r="Q53">
-        <v>40.17966101</v>
+        <v>39.86004652</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.3649211141337482</v>
+        <v>0.3701815301457926</v>
       </c>
       <c r="T53">
-        <v>1.567960805885775</v>
+        <v>1.593807187601787</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.360687101268683</v>
+        <v>2.315289272398132</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2033075344699805</v>
+        <v>0.2026760230144243</v>
       </c>
       <c r="C54">
-        <v>441.1359694494047</v>
+        <v>437.6526698194824</v>
       </c>
       <c r="D54">
-        <v>746.1599694494048</v>
+        <v>749.1636698194825</v>
       </c>
       <c r="E54">
-        <v>70.72399999999999</v>
+        <v>77.21100000000001</v>
       </c>
       <c r="F54">
-        <v>337.324</v>
+        <v>343.811</v>
       </c>
       <c r="G54">
         <v>32.3</v>
@@ -5715,28 +5715,28 @@
         <v>59.2</v>
       </c>
       <c r="M54">
-        <v>25.5691592</v>
+        <v>26.0608738</v>
       </c>
       <c r="N54">
-        <v>33.6308408</v>
+        <v>33.1391262</v>
       </c>
       <c r="O54">
-        <v>11.77079428</v>
+        <v>11.59869417</v>
       </c>
       <c r="P54">
-        <v>21.86004652</v>
+        <v>21.54043203</v>
       </c>
       <c r="Q54">
-        <v>39.86004652</v>
+        <v>39.54043203</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.3701815301457926</v>
+        <v>0.3756657936477113</v>
       </c>
       <c r="T54">
-        <v>1.593807187601787</v>
+        <v>1.620753415348266</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.315289272398132</v>
+        <v>2.271604569145337</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2026760230144243</v>
+        <v>0.2020445115588682</v>
       </c>
       <c r="C55">
-        <v>437.6526698194824</v>
+        <v>434.1936509937155</v>
       </c>
       <c r="D55">
-        <v>749.1636698194825</v>
+        <v>752.1916509937156</v>
       </c>
       <c r="E55">
-        <v>77.21100000000001</v>
+        <v>83.69800000000004</v>
       </c>
       <c r="F55">
-        <v>343.811</v>
+        <v>350.2980000000001</v>
       </c>
       <c r="G55">
         <v>32.3</v>
@@ -5797,28 +5797,28 @@
         <v>59.2</v>
       </c>
       <c r="M55">
-        <v>26.0608738</v>
+        <v>26.55258840000001</v>
       </c>
       <c r="N55">
-        <v>33.1391262</v>
+        <v>32.6474116</v>
       </c>
       <c r="O55">
-        <v>11.59869417</v>
+        <v>11.42659406</v>
       </c>
       <c r="P55">
-        <v>21.54043203</v>
+        <v>21.22081754</v>
       </c>
       <c r="Q55">
-        <v>39.54043203</v>
+        <v>39.22081754</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3756657936477113</v>
+        <v>0.3813885033888438</v>
       </c>
       <c r="T55">
-        <v>1.620753415348266</v>
+        <v>1.648871218214158</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.271604569145337</v>
+        <v>2.229537817864867</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2020445115588682</v>
+        <v>0.201413000103312</v>
       </c>
       <c r="C56">
-        <v>434.1936509937155</v>
+        <v>430.7592085824828</v>
       </c>
       <c r="D56">
-        <v>752.1916509937156</v>
+        <v>755.2442085824829</v>
       </c>
       <c r="E56">
-        <v>83.69800000000004</v>
+        <v>90.18500000000006</v>
       </c>
       <c r="F56">
-        <v>350.2980000000001</v>
+        <v>356.7850000000001</v>
       </c>
       <c r="G56">
         <v>32.3</v>
@@ -5879,28 +5879,28 @@
         <v>59.2</v>
       </c>
       <c r="M56">
-        <v>26.55258840000001</v>
+        <v>27.04430300000001</v>
       </c>
       <c r="N56">
-        <v>32.6474116</v>
+        <v>32.15569699999999</v>
       </c>
       <c r="O56">
-        <v>11.42659406</v>
+        <v>11.25449395</v>
       </c>
       <c r="P56">
-        <v>21.22081754</v>
+        <v>20.90120304999999</v>
       </c>
       <c r="Q56">
-        <v>39.22081754</v>
+        <v>38.90120304999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3813885033888438</v>
+        <v>0.3873655557851378</v>
       </c>
       <c r="T56">
-        <v>1.648871218214158</v>
+        <v>1.678238701207423</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.229537817864867</v>
+        <v>2.189000766630961</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.201413000103312</v>
+        <v>0.2007814886477559</v>
       </c>
       <c r="C57">
-        <v>430.7592085824828</v>
+        <v>427.3496430143219</v>
       </c>
       <c r="D57">
-        <v>755.2442085824829</v>
+        <v>758.321643014322</v>
       </c>
       <c r="E57">
-        <v>90.18500000000006</v>
+        <v>96.67200000000003</v>
       </c>
       <c r="F57">
-        <v>356.7850000000001</v>
+        <v>363.272</v>
       </c>
       <c r="G57">
         <v>32.3</v>
@@ -5961,28 +5961,28 @@
         <v>59.2</v>
       </c>
       <c r="M57">
-        <v>27.04430300000001</v>
+        <v>27.5360176</v>
       </c>
       <c r="N57">
-        <v>32.15569699999999</v>
+        <v>31.6639824</v>
       </c>
       <c r="O57">
-        <v>11.25449395</v>
+        <v>11.08239384</v>
       </c>
       <c r="P57">
-        <v>20.90120304999999</v>
+        <v>20.58158856</v>
       </c>
       <c r="Q57">
-        <v>38.90120304999999</v>
+        <v>38.58158856</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3873655557851378</v>
+        <v>0.3936142923812633</v>
       </c>
       <c r="T57">
-        <v>1.678238701207423</v>
+        <v>1.708941069791291</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.189000766630961</v>
+        <v>2.149911467226836</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2007814886477559</v>
+        <v>0.2001499771921997</v>
       </c>
       <c r="C58">
-        <v>427.3496430143219</v>
+        <v>423.9652596344941</v>
       </c>
       <c r="D58">
-        <v>758.321643014322</v>
+        <v>761.4242596344942</v>
       </c>
       <c r="E58">
-        <v>96.67200000000003</v>
+        <v>103.159</v>
       </c>
       <c r="F58">
-        <v>363.272</v>
+        <v>369.7590000000001</v>
       </c>
       <c r="G58">
         <v>32.3</v>
@@ -6043,28 +6043,28 @@
         <v>59.2</v>
       </c>
       <c r="M58">
-        <v>27.5360176</v>
+        <v>28.02773220000001</v>
       </c>
       <c r="N58">
-        <v>31.6639824</v>
+        <v>31.1722678</v>
       </c>
       <c r="O58">
-        <v>11.08239384</v>
+        <v>10.91029373</v>
       </c>
       <c r="P58">
-        <v>20.58158856</v>
+        <v>20.26197407</v>
       </c>
       <c r="Q58">
-        <v>38.58158856</v>
+        <v>38.26197407</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3936142923812633</v>
+        <v>0.4001536678888366</v>
       </c>
       <c r="T58">
-        <v>1.708941069791291</v>
+        <v>1.741071455518595</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.149911467226836</v>
+        <v>2.112193722187769</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2001499771921997</v>
+        <v>0.1995184657366436</v>
       </c>
       <c r="C59">
-        <v>423.9652596344941</v>
+        <v>420.60636880598</v>
       </c>
       <c r="D59">
-        <v>761.4242596344942</v>
+        <v>764.5523688059801</v>
       </c>
       <c r="E59">
-        <v>103.159</v>
+        <v>109.6460000000001</v>
       </c>
       <c r="F59">
-        <v>369.7590000000001</v>
+        <v>376.2460000000001</v>
       </c>
       <c r="G59">
         <v>32.3</v>
@@ -6125,28 +6125,28 @@
         <v>59.2</v>
       </c>
       <c r="M59">
-        <v>28.02773220000001</v>
+        <v>28.51944680000001</v>
       </c>
       <c r="N59">
-        <v>31.1722678</v>
+        <v>30.68055319999999</v>
       </c>
       <c r="O59">
-        <v>10.91029373</v>
+        <v>10.73819362</v>
       </c>
       <c r="P59">
-        <v>20.26197407</v>
+        <v>19.94235958</v>
       </c>
       <c r="Q59">
-        <v>38.26197407</v>
+        <v>37.94235958</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.4001536678888366</v>
+        <v>0.4070044422301037</v>
       </c>
       <c r="T59">
-        <v>1.741071455518595</v>
+        <v>1.774731859613865</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.112193722187769</v>
+        <v>2.0757765890466</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1995184657366436</v>
+        <v>0.1988869542810874</v>
       </c>
       <c r="C60">
-        <v>420.6063688059801</v>
+        <v>417.2732860129752</v>
       </c>
       <c r="D60">
-        <v>764.5523688059801</v>
+        <v>767.7062860129753</v>
       </c>
       <c r="E60">
-        <v>109.646</v>
+        <v>116.133</v>
       </c>
       <c r="F60">
-        <v>376.246</v>
+        <v>382.733</v>
       </c>
       <c r="G60">
         <v>32.3</v>
@@ -6207,28 +6207,28 @@
         <v>59.2</v>
       </c>
       <c r="M60">
-        <v>28.5194468</v>
+        <v>29.0111614</v>
       </c>
       <c r="N60">
-        <v>30.6805532</v>
+        <v>30.1888386</v>
       </c>
       <c r="O60">
-        <v>10.73819362</v>
+        <v>10.56609351</v>
       </c>
       <c r="P60">
-        <v>19.94235958</v>
+        <v>19.62274509</v>
       </c>
       <c r="Q60">
-        <v>37.94235958</v>
+        <v>37.62274509</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.4070044422301037</v>
+        <v>0.4141894006855789</v>
       </c>
       <c r="T60">
-        <v>1.774731859613865</v>
+        <v>1.810034234640612</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.075776589046601</v>
+        <v>2.040593934994964</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1988869542810874</v>
+        <v>0.1982554428255312</v>
       </c>
       <c r="C61">
-        <v>417.2732860129752</v>
+        <v>413.9663319669557</v>
       </c>
       <c r="D61">
-        <v>767.7062860129753</v>
+        <v>770.8863319669558</v>
       </c>
       <c r="E61">
-        <v>116.133</v>
+        <v>122.62</v>
       </c>
       <c r="F61">
-        <v>382.733</v>
+        <v>389.22</v>
       </c>
       <c r="G61">
         <v>32.3</v>
@@ -6289,28 +6289,28 @@
         <v>59.2</v>
       </c>
       <c r="M61">
-        <v>29.0111614</v>
+        <v>29.502876</v>
       </c>
       <c r="N61">
-        <v>30.1888386</v>
+        <v>29.697124</v>
       </c>
       <c r="O61">
-        <v>10.56609351</v>
+        <v>10.3939934</v>
       </c>
       <c r="P61">
-        <v>19.62274509</v>
+        <v>19.3031306</v>
       </c>
       <c r="Q61">
-        <v>37.62274509</v>
+        <v>37.3031306</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.4141894006855789</v>
+        <v>0.4217336070638281</v>
       </c>
       <c r="T61">
-        <v>1.810034234640612</v>
+        <v>1.847101728418696</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.040593934994964</v>
+        <v>2.006584036078381</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1982554428255312</v>
+        <v>0.2032542313699751</v>
       </c>
       <c r="C62">
-        <v>413.9663319669557</v>
+        <v>383.0055675480746</v>
       </c>
       <c r="D62">
-        <v>770.8863319669558</v>
+        <v>746.4125675480747</v>
       </c>
       <c r="E62">
-        <v>122.62</v>
+        <v>129.107</v>
       </c>
       <c r="F62">
-        <v>389.22</v>
+        <v>395.707</v>
       </c>
       <c r="G62">
         <v>32.3</v>
@@ -6371,45 +6371,45 @@
         <v>59.2</v>
       </c>
       <c r="M62">
-        <v>29.502876</v>
+        <v>35.61363</v>
       </c>
       <c r="N62">
-        <v>29.697124</v>
+        <v>23.58637</v>
       </c>
       <c r="O62">
-        <v>10.3939934</v>
+        <v>8.2552295</v>
       </c>
       <c r="P62">
-        <v>19.3031306</v>
+        <v>15.3311405</v>
       </c>
       <c r="Q62">
-        <v>37.3031306</v>
+        <v>33.3311405</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.4217336070638281</v>
+        <v>0.4296646958204489</v>
       </c>
       <c r="T62">
-        <v>1.847101728418696</v>
+        <v>1.886070119313605</v>
       </c>
       <c r="U62">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V62">
         <v>0.35</v>
       </c>
       <c r="W62">
-        <v>0.04927000000000001</v>
+        <v>0.0585</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y62">
-        <v>2.006584036078381</v>
+        <v>1.662284917319577</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2032542313699751</v>
+        <v>0.202715019914419</v>
       </c>
       <c r="C63">
-        <v>383.0055675480746</v>
+        <v>379.0834858536168</v>
       </c>
       <c r="D63">
-        <v>746.4125675480747</v>
+        <v>748.9774858536168</v>
       </c>
       <c r="E63">
-        <v>129.107</v>
+        <v>135.594</v>
       </c>
       <c r="F63">
-        <v>395.707</v>
+        <v>402.194</v>
       </c>
       <c r="G63">
         <v>32.3</v>
@@ -6453,28 +6453,28 @@
         <v>59.2</v>
       </c>
       <c r="M63">
-        <v>35.61363</v>
+        <v>36.19746</v>
       </c>
       <c r="N63">
-        <v>23.58637</v>
+        <v>23.00254</v>
       </c>
       <c r="O63">
-        <v>8.2552295</v>
+        <v>8.050889000000002</v>
       </c>
       <c r="P63">
-        <v>15.3311405</v>
+        <v>14.951651</v>
       </c>
       <c r="Q63">
-        <v>33.3311405</v>
+        <v>32.951651</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.4296646958204489</v>
+        <v>0.4380132103011025</v>
       </c>
       <c r="T63">
-        <v>1.886070119313605</v>
+        <v>1.927089478150352</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.662284917319577</v>
+        <v>1.635473870266035</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.202715019914419</v>
+        <v>0.2021758084588628</v>
       </c>
       <c r="C64">
-        <v>379.0834858536168</v>
+        <v>375.1790927434297</v>
       </c>
       <c r="D64">
-        <v>748.9774858536168</v>
+        <v>751.5600927434298</v>
       </c>
       <c r="E64">
-        <v>135.594</v>
+        <v>142.081</v>
       </c>
       <c r="F64">
-        <v>402.194</v>
+        <v>408.681</v>
       </c>
       <c r="G64">
         <v>32.3</v>
@@ -6535,28 +6535,28 @@
         <v>59.2</v>
       </c>
       <c r="M64">
-        <v>36.19746</v>
+        <v>36.78129000000001</v>
       </c>
       <c r="N64">
-        <v>23.00254</v>
+        <v>22.41871</v>
       </c>
       <c r="O64">
-        <v>8.050889000000002</v>
+        <v>7.846548499999998</v>
       </c>
       <c r="P64">
-        <v>14.951651</v>
+        <v>14.5721615</v>
       </c>
       <c r="Q64">
-        <v>32.951651</v>
+        <v>32.5721615</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.4380132103011025</v>
+        <v>0.4468129958347642</v>
       </c>
       <c r="T64">
-        <v>1.927089478150352</v>
+        <v>1.970326099626923</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.635473870266035</v>
+        <v>1.6095139675634</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2021758084588628</v>
+        <v>0.2016365970033067</v>
       </c>
       <c r="C65">
-        <v>375.1790927434297</v>
+        <v>371.2925718307487</v>
       </c>
       <c r="D65">
-        <v>751.5600927434298</v>
+        <v>754.1605718307488</v>
       </c>
       <c r="E65">
-        <v>142.081</v>
+        <v>148.568</v>
       </c>
       <c r="F65">
-        <v>408.681</v>
+        <v>415.1680000000001</v>
       </c>
       <c r="G65">
         <v>32.3</v>
@@ -6617,28 +6617,28 @@
         <v>59.2</v>
       </c>
       <c r="M65">
-        <v>36.78129000000001</v>
+        <v>37.36512</v>
       </c>
       <c r="N65">
-        <v>22.41871</v>
+        <v>21.83488</v>
       </c>
       <c r="O65">
-        <v>7.846548499999998</v>
+        <v>7.642207999999999</v>
       </c>
       <c r="P65">
-        <v>14.5721615</v>
+        <v>14.192672</v>
       </c>
       <c r="Q65">
-        <v>32.5721615</v>
+        <v>32.192672</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.4468129958347642</v>
+        <v>0.4561016583425185</v>
       </c>
       <c r="T65">
-        <v>1.970326099626923</v>
+        <v>2.01596475562997</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.6095139675634</v>
+        <v>1.584365311820222</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2016365970033067</v>
+        <v>0.2010973855477505</v>
       </c>
       <c r="C66">
-        <v>371.2925718307487</v>
+        <v>367.4241092789204</v>
       </c>
       <c r="D66">
-        <v>754.1605718307488</v>
+        <v>756.7791092789205</v>
       </c>
       <c r="E66">
-        <v>148.568</v>
+        <v>155.055</v>
       </c>
       <c r="F66">
-        <v>415.1680000000001</v>
+        <v>421.655</v>
       </c>
       <c r="G66">
         <v>32.3</v>
@@ -6699,28 +6699,28 @@
         <v>59.2</v>
       </c>
       <c r="M66">
-        <v>37.36512</v>
+        <v>37.94895</v>
       </c>
       <c r="N66">
-        <v>21.83488</v>
+        <v>21.25105</v>
       </c>
       <c r="O66">
-        <v>7.642207999999999</v>
+        <v>7.437867499999999</v>
       </c>
       <c r="P66">
-        <v>14.192672</v>
+        <v>13.8131825</v>
       </c>
       <c r="Q66">
-        <v>32.192672</v>
+        <v>31.8131825</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.4561016583425185</v>
+        <v>0.4659211015650014</v>
       </c>
       <c r="T66">
-        <v>2.01596475562997</v>
+        <v>2.06421133483319</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.584365311820222</v>
+        <v>1.559990460869141</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2010973855477505</v>
+        <v>0.2005581740921943</v>
       </c>
       <c r="C67">
-        <v>367.4241092789204</v>
+        <v>363.5738938458261</v>
       </c>
       <c r="D67">
-        <v>756.7791092789205</v>
+        <v>759.4158938458262</v>
       </c>
       <c r="E67">
-        <v>155.055</v>
+        <v>161.542</v>
       </c>
       <c r="F67">
-        <v>421.655</v>
+        <v>428.1420000000001</v>
       </c>
       <c r="G67">
         <v>32.3</v>
@@ -6781,28 +6781,28 @@
         <v>59.2</v>
       </c>
       <c r="M67">
-        <v>37.94895</v>
+        <v>38.53278</v>
       </c>
       <c r="N67">
-        <v>21.25105</v>
+        <v>20.66722</v>
       </c>
       <c r="O67">
-        <v>7.437867499999999</v>
+        <v>7.233527</v>
       </c>
       <c r="P67">
-        <v>13.8131825</v>
+        <v>13.433693</v>
       </c>
       <c r="Q67">
-        <v>31.8131825</v>
+        <v>31.433693</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.4659211015650014</v>
+        <v>0.4763181590946892</v>
       </c>
       <c r="T67">
-        <v>2.06421133483319</v>
+        <v>2.115295948107189</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.559990460869141</v>
+        <v>1.536354241765063</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2005581740921943</v>
+        <v>0.2000189626366382</v>
       </c>
       <c r="C68">
-        <v>363.5738938458261</v>
+        <v>359.7421169292406</v>
       </c>
       <c r="D68">
-        <v>759.4158938458262</v>
+        <v>762.0711169292407</v>
       </c>
       <c r="E68">
-        <v>161.542</v>
+        <v>168.0290000000001</v>
       </c>
       <c r="F68">
-        <v>428.1420000000001</v>
+        <v>434.6290000000001</v>
       </c>
       <c r="G68">
         <v>32.3</v>
@@ -6863,28 +6863,28 @@
         <v>59.2</v>
       </c>
       <c r="M68">
-        <v>38.53278</v>
+        <v>39.11661000000001</v>
       </c>
       <c r="N68">
-        <v>20.66722</v>
+        <v>20.08338999999999</v>
       </c>
       <c r="O68">
-        <v>7.233527</v>
+        <v>7.029186499999997</v>
       </c>
       <c r="P68">
-        <v>13.433693</v>
+        <v>13.0542035</v>
       </c>
       <c r="Q68">
-        <v>31.433693</v>
+        <v>31.0542035</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.4763181590946892</v>
+        <v>0.4873453413231461</v>
       </c>
       <c r="T68">
-        <v>2.115295948107189</v>
+        <v>2.169476598549309</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.536354241765063</v>
+        <v>1.513423581440211</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2000189626366382</v>
+        <v>0.2314697357846098</v>
       </c>
       <c r="C69">
-        <v>359.7421169292406</v>
+        <v>224.1671655736835</v>
       </c>
       <c r="D69">
-        <v>762.0711169292407</v>
+        <v>632.9831655736836</v>
       </c>
       <c r="E69">
-        <v>168.0290000000001</v>
+        <v>174.516</v>
       </c>
       <c r="F69">
-        <v>434.6290000000001</v>
+        <v>441.116</v>
       </c>
       <c r="G69">
         <v>32.3</v>
@@ -6945,45 +6945,45 @@
         <v>59.2</v>
       </c>
       <c r="M69">
-        <v>39.11661000000001</v>
+        <v>64.75582880000002</v>
       </c>
       <c r="N69">
-        <v>20.08338999999999</v>
+        <v>-5.555828800000015</v>
       </c>
       <c r="O69">
-        <v>7.029186499999997</v>
+        <v>-1.944540080000005</v>
       </c>
       <c r="P69">
-        <v>13.0542035</v>
+        <v>-3.61128872000001</v>
       </c>
       <c r="Q69">
-        <v>31.0542035</v>
+        <v>14.38871127999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.4873453413231461</v>
+        <v>0.5112079389715796</v>
       </c>
       <c r="T69">
-        <v>2.169476598549309</v>
+        <v>2.286722422101067</v>
       </c>
       <c r="U69">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.35</v>
+        <v>0.3199711961682127</v>
       </c>
       <c r="W69">
-        <v>0.0585</v>
+        <v>0.09982822840250639</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y69">
-        <v>1.513423581440211</v>
+        <v>0.9142034176234648</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2314697357846098</v>
+        <v>0.2324797357846098</v>
       </c>
       <c r="C70">
-        <v>224.1671655736835</v>
+        <v>214.2555142876593</v>
       </c>
       <c r="D70">
-        <v>632.9831655736836</v>
+        <v>629.5585142876594</v>
       </c>
       <c r="E70">
-        <v>174.516</v>
+        <v>181.003</v>
       </c>
       <c r="F70">
-        <v>441.116</v>
+        <v>447.6030000000001</v>
       </c>
       <c r="G70">
         <v>32.3</v>
@@ -7027,37 +7027,37 @@
         <v>59.2</v>
       </c>
       <c r="M70">
-        <v>64.75582880000002</v>
+        <v>65.70812040000001</v>
       </c>
       <c r="N70">
-        <v>-5.555828800000015</v>
+        <v>-6.50812040000001</v>
       </c>
       <c r="O70">
-        <v>-1.944540080000005</v>
+        <v>-2.277842140000003</v>
       </c>
       <c r="P70">
-        <v>-3.61128872000001</v>
+        <v>-4.230278260000007</v>
       </c>
       <c r="Q70">
-        <v>14.38871127999999</v>
+        <v>13.76972173999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.5112079389715796</v>
+        <v>0.5262210982932434</v>
       </c>
       <c r="T70">
-        <v>2.286722422101067</v>
+        <v>2.360487661523682</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.3199711961682127</v>
+        <v>0.3153339324556299</v>
       </c>
       <c r="W70">
-        <v>0.09982822840250639</v>
+        <v>0.1005089787155135</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.9142034176234648</v>
+        <v>0.9009540927303712</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2324797357846098</v>
+        <v>0.2334897357846098</v>
       </c>
       <c r="C71">
-        <v>214.2555142876593</v>
+        <v>204.38072061438</v>
       </c>
       <c r="D71">
-        <v>629.5585142876594</v>
+        <v>626.1707206143801</v>
       </c>
       <c r="E71">
-        <v>181.003</v>
+        <v>187.4900000000001</v>
       </c>
       <c r="F71">
-        <v>447.6030000000001</v>
+        <v>454.0900000000001</v>
       </c>
       <c r="G71">
         <v>32.3</v>
@@ -7109,37 +7109,37 @@
         <v>59.2</v>
       </c>
       <c r="M71">
-        <v>65.70812040000001</v>
+        <v>66.66041200000002</v>
       </c>
       <c r="N71">
-        <v>-6.50812040000001</v>
+        <v>-7.460412000000019</v>
       </c>
       <c r="O71">
-        <v>-2.277842140000003</v>
+        <v>-2.611144200000007</v>
       </c>
       <c r="P71">
-        <v>-4.230278260000007</v>
+        <v>-4.849267800000012</v>
       </c>
       <c r="Q71">
-        <v>13.76972173999999</v>
+        <v>13.15073219999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.5262210982932434</v>
+        <v>0.5422351349030182</v>
       </c>
       <c r="T71">
-        <v>2.360487661523682</v>
+        <v>2.439170583574471</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.3153339324556299</v>
+        <v>0.310829161991978</v>
       </c>
       <c r="W71">
-        <v>0.1005089787155135</v>
+        <v>0.1011702790195776</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.9009540927303712</v>
+        <v>0.88808331997708</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2334897357846098</v>
+        <v>0.2344997357846098</v>
       </c>
       <c r="C72">
-        <v>204.38072061438</v>
+        <v>194.5421927217156</v>
       </c>
       <c r="D72">
-        <v>626.1707206143801</v>
+        <v>622.8191927217157</v>
       </c>
       <c r="E72">
-        <v>187.4900000000001</v>
+        <v>193.977</v>
       </c>
       <c r="F72">
-        <v>454.0900000000001</v>
+        <v>460.5770000000001</v>
       </c>
       <c r="G72">
         <v>32.3</v>
@@ -7191,37 +7191,37 @@
         <v>59.2</v>
       </c>
       <c r="M72">
-        <v>66.66041200000002</v>
+        <v>67.61270360000002</v>
       </c>
       <c r="N72">
-        <v>-7.460412000000019</v>
+        <v>-8.412703600000015</v>
       </c>
       <c r="O72">
-        <v>-2.611144200000007</v>
+        <v>-2.944446260000005</v>
       </c>
       <c r="P72">
-        <v>-4.849267800000012</v>
+        <v>-5.46825734000001</v>
       </c>
       <c r="Q72">
-        <v>13.15073219999999</v>
+        <v>12.53174265999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.5422351349030182</v>
+        <v>0.5593535878307085</v>
       </c>
       <c r="T72">
-        <v>2.439170583574471</v>
+        <v>2.523279914042557</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.310829161991978</v>
+        <v>0.3064512864709642</v>
       </c>
       <c r="W72">
-        <v>0.1011702790195776</v>
+        <v>0.1018129511460625</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.88808331997708</v>
+        <v>0.875575104202755</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2344997357846098</v>
+        <v>0.2355097357846098</v>
       </c>
       <c r="C73">
-        <v>194.5421927217158</v>
+        <v>184.7393513810101</v>
       </c>
       <c r="D73">
-        <v>622.8191927217158</v>
+        <v>619.5033513810101</v>
       </c>
       <c r="E73">
-        <v>193.977</v>
+        <v>200.464</v>
       </c>
       <c r="F73">
-        <v>460.577</v>
+        <v>467.064</v>
       </c>
       <c r="G73">
         <v>32.3</v>
@@ -7273,37 +7273,37 @@
         <v>59.2</v>
       </c>
       <c r="M73">
-        <v>67.6127036</v>
+        <v>68.56499520000001</v>
       </c>
       <c r="N73">
-        <v>-8.4127036</v>
+        <v>-9.36499520000001</v>
       </c>
       <c r="O73">
-        <v>-2.94444626</v>
+        <v>-3.277748320000003</v>
       </c>
       <c r="P73">
-        <v>-5.468257340000001</v>
+        <v>-6.087246880000007</v>
       </c>
       <c r="Q73">
-        <v>12.53174266</v>
+        <v>11.91275311999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.5593535878307082</v>
+        <v>0.5776947873960908</v>
       </c>
       <c r="T73">
-        <v>2.523279914042555</v>
+        <v>2.61339705382979</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.3064512864709643</v>
+        <v>0.302195018603312</v>
       </c>
       <c r="W73">
-        <v>0.1018129511460625</v>
+        <v>0.1024377712690338</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8755751042027552</v>
+        <v>0.8634143388666057</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2355097357846098</v>
+        <v>0.2365197357846098</v>
       </c>
       <c r="C74">
-        <v>184.7393513810101</v>
+        <v>174.9716296333592</v>
       </c>
       <c r="D74">
-        <v>619.5033513810101</v>
+        <v>616.2226296333592</v>
       </c>
       <c r="E74">
-        <v>200.464</v>
+        <v>206.951</v>
       </c>
       <c r="F74">
-        <v>467.064</v>
+        <v>473.551</v>
       </c>
       <c r="G74">
         <v>32.3</v>
@@ -7355,37 +7355,37 @@
         <v>59.2</v>
       </c>
       <c r="M74">
-        <v>68.56499520000001</v>
+        <v>69.51728680000001</v>
       </c>
       <c r="N74">
-        <v>-9.36499520000001</v>
+        <v>-10.31728680000001</v>
       </c>
       <c r="O74">
-        <v>-3.277748320000003</v>
+        <v>-3.611050380000001</v>
       </c>
       <c r="P74">
-        <v>-6.087246880000007</v>
+        <v>-6.706236420000003</v>
       </c>
       <c r="Q74">
-        <v>11.91275311999999</v>
+        <v>11.29376358</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.5776947873960908</v>
+        <v>0.5973945943366867</v>
       </c>
       <c r="T74">
-        <v>2.61339705382979</v>
+        <v>2.710189537304967</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.302195018603312</v>
+        <v>0.2980553608142255</v>
       </c>
       <c r="W74">
-        <v>0.1024377712690338</v>
+        <v>0.1030454730324717</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8634143388666057</v>
+        <v>0.8515867451835015</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2365197357846098</v>
+        <v>0.2375297357846097</v>
       </c>
       <c r="C75">
-        <v>174.9716296333592</v>
+        <v>165.2384724664352</v>
       </c>
       <c r="D75">
-        <v>616.2226296333592</v>
+        <v>612.9764724664352</v>
       </c>
       <c r="E75">
-        <v>206.951</v>
+        <v>213.438</v>
       </c>
       <c r="F75">
-        <v>473.551</v>
+        <v>480.038</v>
       </c>
       <c r="G75">
         <v>32.3</v>
@@ -7437,37 +7437,37 @@
         <v>59.2</v>
       </c>
       <c r="M75">
-        <v>69.51728680000001</v>
+        <v>70.4695784</v>
       </c>
       <c r="N75">
-        <v>-10.31728680000001</v>
+        <v>-11.2695784</v>
       </c>
       <c r="O75">
-        <v>-3.611050380000001</v>
+        <v>-3.94435244</v>
       </c>
       <c r="P75">
-        <v>-6.706236420000003</v>
+        <v>-7.325225960000001</v>
       </c>
       <c r="Q75">
-        <v>11.29376358</v>
+        <v>10.67477404</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.5973945943366867</v>
+        <v>0.6186097710419438</v>
       </c>
       <c r="T75">
-        <v>2.710189537304967</v>
+        <v>2.814427596432081</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.2980553608142255</v>
+        <v>0.2940275856680873</v>
       </c>
       <c r="W75">
-        <v>0.1030454730324717</v>
+        <v>0.1036367504239248</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8515867451835015</v>
+        <v>0.8400788161945354</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2375297357846097</v>
+        <v>0.2385397357846097</v>
       </c>
       <c r="C76">
-        <v>165.2384724664352</v>
+        <v>155.5393365014726</v>
       </c>
       <c r="D76">
-        <v>612.9764724664352</v>
+        <v>609.7643365014727</v>
       </c>
       <c r="E76">
-        <v>213.438</v>
+        <v>219.925</v>
       </c>
       <c r="F76">
-        <v>480.038</v>
+        <v>486.525</v>
       </c>
       <c r="G76">
         <v>32.3</v>
@@ -7519,37 +7519,37 @@
         <v>59.2</v>
       </c>
       <c r="M76">
-        <v>70.4695784</v>
+        <v>71.42187000000001</v>
       </c>
       <c r="N76">
-        <v>-11.2695784</v>
+        <v>-12.22187000000001</v>
       </c>
       <c r="O76">
-        <v>-3.94435244</v>
+        <v>-4.277654500000003</v>
       </c>
       <c r="P76">
-        <v>-7.325225960000001</v>
+        <v>-7.944215500000007</v>
       </c>
       <c r="Q76">
-        <v>10.67477404</v>
+        <v>10.05578449999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.6186097710419438</v>
+        <v>0.6415221618836217</v>
       </c>
       <c r="T76">
-        <v>2.814427596432081</v>
+        <v>2.927004700289365</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.2940275856680873</v>
+        <v>0.2901072178591795</v>
       </c>
       <c r="W76">
-        <v>0.1036367504239248</v>
+        <v>0.1042122604182725</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8400788161945354</v>
+        <v>0.8288777653119415</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2385397357846097</v>
+        <v>0.2395497357846098</v>
       </c>
       <c r="C77">
-        <v>155.5393365014726</v>
+        <v>145.8736896900459</v>
       </c>
       <c r="D77">
-        <v>609.7643365014727</v>
+        <v>606.585689690046</v>
       </c>
       <c r="E77">
-        <v>219.925</v>
+        <v>226.412</v>
       </c>
       <c r="F77">
-        <v>486.525</v>
+        <v>493.0120000000001</v>
       </c>
       <c r="G77">
         <v>32.3</v>
@@ -7601,37 +7601,37 @@
         <v>59.2</v>
       </c>
       <c r="M77">
-        <v>71.42187000000001</v>
+        <v>72.37416160000002</v>
       </c>
       <c r="N77">
-        <v>-12.22187000000001</v>
+        <v>-13.17416160000002</v>
       </c>
       <c r="O77">
-        <v>-4.277654500000003</v>
+        <v>-4.610956560000006</v>
       </c>
       <c r="P77">
-        <v>-7.944215500000007</v>
+        <v>-8.563205040000014</v>
       </c>
       <c r="Q77">
-        <v>10.05578449999999</v>
+        <v>9.436794959999986</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.6415221618836217</v>
+        <v>0.6663439186287726</v>
       </c>
       <c r="T77">
-        <v>2.927004700289365</v>
+        <v>3.048963229468089</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.2901072178591795</v>
+        <v>0.2862900176241903</v>
       </c>
       <c r="W77">
-        <v>0.1042122604182725</v>
+        <v>0.1047726254127689</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8288777653119415</v>
+        <v>0.8179714789262579</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2395497357846098</v>
+        <v>0.2405597357846098</v>
       </c>
       <c r="C78">
-        <v>145.8736896900459</v>
+        <v>136.2410110202799</v>
       </c>
       <c r="D78">
-        <v>606.585689690046</v>
+        <v>603.4400110202799</v>
       </c>
       <c r="E78">
-        <v>226.412</v>
+        <v>232.899</v>
       </c>
       <c r="F78">
-        <v>493.0120000000001</v>
+        <v>499.499</v>
       </c>
       <c r="G78">
         <v>32.3</v>
@@ -7683,37 +7683,37 @@
         <v>59.2</v>
       </c>
       <c r="M78">
-        <v>72.37416160000002</v>
+        <v>73.32645320000002</v>
       </c>
       <c r="N78">
-        <v>-13.17416160000002</v>
+        <v>-14.12645320000001</v>
       </c>
       <c r="O78">
-        <v>-4.610956560000006</v>
+        <v>-4.944258620000005</v>
       </c>
       <c r="P78">
-        <v>-8.563205040000014</v>
+        <v>-9.18219458000001</v>
       </c>
       <c r="Q78">
-        <v>9.436794959999986</v>
+        <v>8.81780541999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.6663439186287726</v>
+        <v>0.6933240890039366</v>
       </c>
       <c r="T78">
-        <v>3.048963229468089</v>
+        <v>3.181526848140614</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.2862900176241903</v>
+        <v>0.2825719654472527</v>
       </c>
       <c r="W78">
-        <v>0.1047726254127689</v>
+        <v>0.1053184354723433</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8179714789262579</v>
+        <v>0.8073484727064364</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2405597357846098</v>
+        <v>0.2948273943660427</v>
       </c>
       <c r="C79">
-        <v>136.2410110202799</v>
+        <v>-1.746688233272039</v>
       </c>
       <c r="D79">
-        <v>603.4400110202799</v>
+        <v>471.939311766728</v>
       </c>
       <c r="E79">
-        <v>232.899</v>
+        <v>239.386</v>
       </c>
       <c r="F79">
-        <v>499.499</v>
+        <v>505.986</v>
       </c>
       <c r="G79">
         <v>32.3</v>
@@ -7765,45 +7765,45 @@
         <v>59.2</v>
       </c>
       <c r="M79">
-        <v>73.32645320000002</v>
+        <v>101.6019888</v>
       </c>
       <c r="N79">
-        <v>-14.12645320000001</v>
+        <v>-42.40198880000001</v>
       </c>
       <c r="O79">
-        <v>-4.944258620000005</v>
+        <v>-14.84069608</v>
       </c>
       <c r="P79">
-        <v>-9.18219458000001</v>
+        <v>-27.56129272000001</v>
       </c>
       <c r="Q79">
-        <v>8.81780541999999</v>
+        <v>-9.561292720000012</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.6933240890039366</v>
+        <v>0.7733827229651742</v>
       </c>
       <c r="T79">
-        <v>3.181526848140614</v>
+        <v>3.574884713428605</v>
       </c>
       <c r="U79">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.2825719654472527</v>
+        <v>0.2039330159253733</v>
       </c>
       <c r="W79">
-        <v>0.1053184354723433</v>
+        <v>0.1598502504021851</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.8073484727064364</v>
+        <v>0.5826657597867808</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2948273943660427</v>
+        <v>0.2963773943660427</v>
       </c>
       <c r="C80">
-        <v>-1.746688233272039</v>
+        <v>-11.15296965963194</v>
       </c>
       <c r="D80">
-        <v>471.939311766728</v>
+        <v>469.0200303403681</v>
       </c>
       <c r="E80">
-        <v>239.386</v>
+        <v>245.873</v>
       </c>
       <c r="F80">
-        <v>505.986</v>
+        <v>512.4730000000001</v>
       </c>
       <c r="G80">
         <v>32.3</v>
@@ -7847,37 +7847,37 @@
         <v>59.2</v>
       </c>
       <c r="M80">
-        <v>101.6019888</v>
+        <v>102.9045784</v>
       </c>
       <c r="N80">
-        <v>-42.40198880000001</v>
+        <v>-43.70457840000002</v>
       </c>
       <c r="O80">
-        <v>-14.84069608</v>
+        <v>-15.29660244</v>
       </c>
       <c r="P80">
-        <v>-27.56129272000001</v>
+        <v>-28.40797596000001</v>
       </c>
       <c r="Q80">
-        <v>-9.561292720000012</v>
+        <v>-10.40797596000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.7733827229651742</v>
+        <v>0.8080295192968493</v>
       </c>
       <c r="T80">
-        <v>3.574884713428605</v>
+        <v>3.745117318829967</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.2039330159253733</v>
+        <v>0.2013515853440394</v>
       </c>
       <c r="W80">
-        <v>0.1598502504021851</v>
+        <v>0.1603686016629169</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5826657597867808</v>
+        <v>0.5752902438401126</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2963773943660427</v>
+        <v>0.2979273943660427</v>
       </c>
       <c r="C81">
-        <v>-11.15296965963194</v>
+        <v>-20.52335743609905</v>
       </c>
       <c r="D81">
-        <v>469.0200303403681</v>
+        <v>466.136642563901</v>
       </c>
       <c r="E81">
-        <v>245.873</v>
+        <v>252.36</v>
       </c>
       <c r="F81">
-        <v>512.4730000000001</v>
+        <v>518.96</v>
       </c>
       <c r="G81">
         <v>32.3</v>
@@ -7929,37 +7929,37 @@
         <v>59.2</v>
       </c>
       <c r="M81">
-        <v>102.9045784</v>
+        <v>104.207168</v>
       </c>
       <c r="N81">
-        <v>-43.70457840000002</v>
+        <v>-45.00716800000001</v>
       </c>
       <c r="O81">
-        <v>-15.29660244</v>
+        <v>-15.7525088</v>
       </c>
       <c r="P81">
-        <v>-28.40797596000001</v>
+        <v>-29.25465920000001</v>
       </c>
       <c r="Q81">
-        <v>-10.40797596000001</v>
+        <v>-11.25465920000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.8080295192968493</v>
+        <v>0.8461409952616917</v>
       </c>
       <c r="T81">
-        <v>3.745117318829967</v>
+        <v>3.932373184771466</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.2013515853440394</v>
+        <v>0.198834690527239</v>
       </c>
       <c r="W81">
-        <v>0.1603686016629169</v>
+        <v>0.1608739941421304</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5752902438401126</v>
+        <v>0.5680991157921114</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2979273943660427</v>
+        <v>0.2994773943660426</v>
       </c>
       <c r="C82">
-        <v>-20.52335743609905</v>
+        <v>-29.8585095064862</v>
       </c>
       <c r="D82">
-        <v>466.136642563901</v>
+        <v>463.2884904935139</v>
       </c>
       <c r="E82">
-        <v>252.36</v>
+        <v>258.8470000000001</v>
       </c>
       <c r="F82">
-        <v>518.96</v>
+        <v>525.4470000000001</v>
       </c>
       <c r="G82">
         <v>32.3</v>
@@ -8011,37 +8011,37 @@
         <v>59.2</v>
       </c>
       <c r="M82">
-        <v>104.207168</v>
+        <v>105.5097576</v>
       </c>
       <c r="N82">
-        <v>-45.00716800000001</v>
+        <v>-46.30975760000003</v>
       </c>
       <c r="O82">
-        <v>-15.7525088</v>
+        <v>-16.20841516000001</v>
       </c>
       <c r="P82">
-        <v>-29.25465920000001</v>
+        <v>-30.10134244000002</v>
       </c>
       <c r="Q82">
-        <v>-11.25465920000001</v>
+        <v>-12.10134244000002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.8461409952616917</v>
+        <v>0.8882642055386228</v>
       </c>
       <c r="T82">
-        <v>3.932373184771466</v>
+        <v>4.139340194496279</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.198834690527239</v>
+        <v>0.1963799412614705</v>
       </c>
       <c r="W82">
-        <v>0.1608739941421304</v>
+        <v>0.1613669077946967</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5680991157921114</v>
+        <v>0.5610855464613445</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2994773943660426</v>
+        <v>0.3010273943660426</v>
       </c>
       <c r="C83">
-        <v>-29.8585095064862</v>
+        <v>-39.15906783179304</v>
       </c>
       <c r="D83">
-        <v>463.2884904935139</v>
+        <v>460.474932168207</v>
       </c>
       <c r="E83">
-        <v>258.8470000000001</v>
+        <v>265.3340000000001</v>
       </c>
       <c r="F83">
-        <v>525.4470000000001</v>
+        <v>531.9340000000001</v>
       </c>
       <c r="G83">
         <v>32.3</v>
@@ -8093,37 +8093,37 @@
         <v>59.2</v>
       </c>
       <c r="M83">
-        <v>105.5097576</v>
+        <v>106.8123472</v>
       </c>
       <c r="N83">
-        <v>-46.30975760000003</v>
+        <v>-47.61234720000002</v>
       </c>
       <c r="O83">
-        <v>-16.20841516000001</v>
+        <v>-16.66432152</v>
       </c>
       <c r="P83">
-        <v>-30.10134244000002</v>
+        <v>-30.94802568000001</v>
       </c>
       <c r="Q83">
-        <v>-12.10134244000002</v>
+        <v>-12.94802568000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.8882642055386228</v>
+        <v>0.9350677725129908</v>
       </c>
       <c r="T83">
-        <v>4.139340194496279</v>
+        <v>4.369303538634962</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1963799412614705</v>
+        <v>0.1939850639290136</v>
       </c>
       <c r="W83">
-        <v>0.1613669077946967</v>
+        <v>0.1618477991630541</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5610855464613445</v>
+        <v>0.5542430397971817</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.3010273943660426</v>
+        <v>0.3025773943660426</v>
       </c>
       <c r="C84">
-        <v>-39.15906783179304</v>
+        <v>-48.42565887259639</v>
       </c>
       <c r="D84">
-        <v>460.474932168207</v>
+        <v>457.6953411274037</v>
       </c>
       <c r="E84">
-        <v>265.3340000000001</v>
+        <v>271.821</v>
       </c>
       <c r="F84">
-        <v>531.9340000000001</v>
+        <v>538.421</v>
       </c>
       <c r="G84">
         <v>32.3</v>
@@ -8175,37 +8175,37 @@
         <v>59.2</v>
       </c>
       <c r="M84">
-        <v>106.8123472</v>
+        <v>108.1149368</v>
       </c>
       <c r="N84">
-        <v>-47.61234720000002</v>
+        <v>-48.91493680000001</v>
       </c>
       <c r="O84">
-        <v>-16.66432152</v>
+        <v>-17.12022788</v>
       </c>
       <c r="P84">
-        <v>-30.94802568000001</v>
+        <v>-31.79470892000001</v>
       </c>
       <c r="Q84">
-        <v>-12.94802568000001</v>
+        <v>-13.79470892000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.9350677725129908</v>
+        <v>0.9873776414843431</v>
       </c>
       <c r="T84">
-        <v>4.369303538634962</v>
+        <v>4.626321393848783</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1939850639290136</v>
+        <v>0.1916478944840858</v>
       </c>
       <c r="W84">
-        <v>0.1618477991630541</v>
+        <v>0.1623171027875956</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5542430397971817</v>
+        <v>0.5475654128116736</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.3025773943660426</v>
+        <v>0.3041273943660427</v>
       </c>
       <c r="C85">
-        <v>-48.42565887259639</v>
+        <v>-57.65889405407427</v>
       </c>
       <c r="D85">
-        <v>457.6953411274037</v>
+        <v>454.9491059459259</v>
       </c>
       <c r="E85">
-        <v>271.821</v>
+        <v>278.3080000000001</v>
       </c>
       <c r="F85">
-        <v>538.421</v>
+        <v>544.9080000000001</v>
       </c>
       <c r="G85">
         <v>32.3</v>
@@ -8257,37 +8257,37 @@
         <v>59.2</v>
       </c>
       <c r="M85">
-        <v>108.1149368</v>
+        <v>109.4175264</v>
       </c>
       <c r="N85">
-        <v>-48.91493680000001</v>
+        <v>-50.21752640000003</v>
       </c>
       <c r="O85">
-        <v>-17.12022788</v>
+        <v>-17.57613424000001</v>
       </c>
       <c r="P85">
-        <v>-31.79470892000001</v>
+        <v>-32.64139216000002</v>
       </c>
       <c r="Q85">
-        <v>-13.79470892000001</v>
+        <v>-14.64139216000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.9873776414843431</v>
+        <v>1.046226244077115</v>
       </c>
       <c r="T85">
-        <v>4.626321393848783</v>
+        <v>4.915466480964334</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1916478944840858</v>
+        <v>0.1893663719307037</v>
       </c>
       <c r="W85">
-        <v>0.1623171027875956</v>
+        <v>0.1627752325163147</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5475654128116736</v>
+        <v>0.5410467769448679</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.3041273943660426</v>
+        <v>0.3056773943660426</v>
       </c>
       <c r="C86">
-        <v>-57.6588940540741</v>
+        <v>-66.85937021438576</v>
       </c>
       <c r="D86">
-        <v>454.9491059459259</v>
+        <v>452.2356297856142</v>
       </c>
       <c r="E86">
-        <v>278.308</v>
+        <v>284.795</v>
       </c>
       <c r="F86">
-        <v>544.908</v>
+        <v>551.395</v>
       </c>
       <c r="G86">
         <v>32.3</v>
@@ -8339,37 +8339,37 @@
         <v>59.2</v>
       </c>
       <c r="M86">
-        <v>109.4175264</v>
+        <v>110.720116</v>
       </c>
       <c r="N86">
-        <v>-50.2175264</v>
+        <v>-51.520116</v>
       </c>
       <c r="O86">
-        <v>-17.57613424</v>
+        <v>-18.0320406</v>
       </c>
       <c r="P86">
-        <v>-32.64139216</v>
+        <v>-33.4880754</v>
       </c>
       <c r="Q86">
-        <v>-14.64139216</v>
+        <v>-15.4880754</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>1.046226244077114</v>
+        <v>1.112921327015589</v>
       </c>
       <c r="T86">
-        <v>4.915466480964329</v>
+        <v>5.243164246361952</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1893663719307038</v>
+        <v>0.1871385322609308</v>
       </c>
       <c r="W86">
-        <v>0.1627752325163147</v>
+        <v>0.1632225827220051</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5410467769448679</v>
+        <v>0.5346815207455166</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.3056773943660426</v>
+        <v>0.3072273943660427</v>
       </c>
       <c r="C87">
-        <v>-66.85937021438576</v>
+        <v>-76.02767003710551</v>
       </c>
       <c r="D87">
-        <v>452.2356297856142</v>
+        <v>449.5543299628945</v>
       </c>
       <c r="E87">
-        <v>284.795</v>
+        <v>291.282</v>
       </c>
       <c r="F87">
-        <v>551.395</v>
+        <v>557.8820000000001</v>
       </c>
       <c r="G87">
         <v>32.3</v>
@@ -8421,37 +8421,37 @@
         <v>59.2</v>
       </c>
       <c r="M87">
-        <v>110.720116</v>
+        <v>112.0227056</v>
       </c>
       <c r="N87">
-        <v>-51.520116</v>
+        <v>-52.82270560000001</v>
       </c>
       <c r="O87">
-        <v>-18.0320406</v>
+        <v>-18.48794696</v>
       </c>
       <c r="P87">
-        <v>-33.4880754</v>
+        <v>-34.33475864</v>
       </c>
       <c r="Q87">
-        <v>-15.4880754</v>
+        <v>-16.33475864</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>1.112921327015589</v>
+        <v>1.189144278945274</v>
       </c>
       <c r="T87">
-        <v>5.243164246361952</v>
+        <v>5.617675978244949</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1871385322609308</v>
+        <v>0.1849625028160362</v>
       </c>
       <c r="W87">
-        <v>0.1632225827220051</v>
+        <v>0.1636595294345399</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5346815207455166</v>
+        <v>0.5284642937601036</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3072273943660427</v>
+        <v>0.3087773943660427</v>
       </c>
       <c r="C88">
-        <v>-76.02767003710551</v>
+        <v>-85.16436246835895</v>
       </c>
       <c r="D88">
-        <v>449.5543299628945</v>
+        <v>446.9046375316411</v>
       </c>
       <c r="E88">
-        <v>291.282</v>
+        <v>297.769</v>
       </c>
       <c r="F88">
-        <v>557.8820000000001</v>
+        <v>564.369</v>
       </c>
       <c r="G88">
         <v>32.3</v>
@@ -8503,37 +8503,37 @@
         <v>59.2</v>
       </c>
       <c r="M88">
-        <v>112.0227056</v>
+        <v>113.3252952</v>
       </c>
       <c r="N88">
-        <v>-52.82270560000001</v>
+        <v>-54.12529520000001</v>
       </c>
       <c r="O88">
-        <v>-18.48794696</v>
+        <v>-18.94385332</v>
       </c>
       <c r="P88">
-        <v>-34.33475864</v>
+        <v>-35.18144188000001</v>
       </c>
       <c r="Q88">
-        <v>-16.33475864</v>
+        <v>-17.18144188000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>1.189144278945274</v>
+        <v>1.277093838864141</v>
       </c>
       <c r="T88">
-        <v>5.617675978244949</v>
+        <v>6.049804899648406</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1849625028160362</v>
+        <v>0.1828364970365416</v>
       </c>
       <c r="W88">
-        <v>0.1636595294345399</v>
+        <v>0.1640864313950625</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5284642937601036</v>
+        <v>0.5223899915329759</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3087773943660427</v>
+        <v>0.3103273943660426</v>
       </c>
       <c r="C89">
-        <v>-85.16436246835895</v>
+        <v>-94.27000311929839</v>
       </c>
       <c r="D89">
-        <v>446.9046375316411</v>
+        <v>444.2859968807016</v>
       </c>
       <c r="E89">
-        <v>297.769</v>
+        <v>304.256</v>
       </c>
       <c r="F89">
-        <v>564.369</v>
+        <v>570.856</v>
       </c>
       <c r="G89">
         <v>32.3</v>
@@ -8585,37 +8585,37 @@
         <v>59.2</v>
       </c>
       <c r="M89">
-        <v>113.3252952</v>
+        <v>114.6278848</v>
       </c>
       <c r="N89">
-        <v>-54.12529520000001</v>
+        <v>-55.4278848</v>
       </c>
       <c r="O89">
-        <v>-18.94385332</v>
+        <v>-19.39975968</v>
       </c>
       <c r="P89">
-        <v>-35.18144188000001</v>
+        <v>-36.02812512</v>
       </c>
       <c r="Q89">
-        <v>-17.18144188000001</v>
+        <v>-18.02812512</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.277093838864141</v>
+        <v>1.379701658769486</v>
       </c>
       <c r="T89">
-        <v>6.049804899648406</v>
+        <v>6.553955307952441</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1828364970365416</v>
+        <v>0.1807588095702172</v>
       </c>
       <c r="W89">
-        <v>0.1640864313950625</v>
+        <v>0.1645036310383004</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5223899915329759</v>
+        <v>0.5164537416291921</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3103273943660426</v>
+        <v>0.3118773943660427</v>
       </c>
       <c r="C90">
-        <v>-94.27000311929839</v>
+        <v>-103.345134654508</v>
       </c>
       <c r="D90">
-        <v>444.2859968807016</v>
+        <v>441.6978653454921</v>
       </c>
       <c r="E90">
-        <v>304.256</v>
+        <v>310.7430000000001</v>
       </c>
       <c r="F90">
-        <v>570.856</v>
+        <v>577.3430000000001</v>
       </c>
       <c r="G90">
         <v>32.3</v>
@@ -8667,37 +8667,37 @@
         <v>59.2</v>
       </c>
       <c r="M90">
-        <v>114.6278848</v>
+        <v>115.9304744</v>
       </c>
       <c r="N90">
-        <v>-55.4278848</v>
+        <v>-56.73047440000002</v>
       </c>
       <c r="O90">
-        <v>-19.39975968</v>
+        <v>-19.85566604000001</v>
       </c>
       <c r="P90">
-        <v>-36.02812512</v>
+        <v>-36.87480836000002</v>
       </c>
       <c r="Q90">
-        <v>-18.02812512</v>
+        <v>-18.87480836000002</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.379701658769486</v>
+        <v>1.500965445930349</v>
       </c>
       <c r="T90">
-        <v>6.553955307952441</v>
+        <v>7.149769426857209</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1807588095702172</v>
+        <v>0.1787278117098777</v>
       </c>
       <c r="W90">
-        <v>0.1645036310383004</v>
+        <v>0.1649114554086566</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5164537416291921</v>
+        <v>0.5106508905996505</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3118773943660427</v>
+        <v>0.3134273943660427</v>
       </c>
       <c r="C91">
-        <v>-103.345134654508</v>
+        <v>-112.3902871669114</v>
       </c>
       <c r="D91">
-        <v>441.6978653454921</v>
+        <v>439.1397128330886</v>
       </c>
       <c r="E91">
-        <v>310.7430000000001</v>
+        <v>317.23</v>
       </c>
       <c r="F91">
-        <v>577.3430000000001</v>
+        <v>583.83</v>
       </c>
       <c r="G91">
         <v>32.3</v>
@@ -8749,37 +8749,37 @@
         <v>59.2</v>
       </c>
       <c r="M91">
-        <v>115.9304744</v>
+        <v>117.233064</v>
       </c>
       <c r="N91">
-        <v>-56.73047440000002</v>
+        <v>-58.03306400000001</v>
       </c>
       <c r="O91">
-        <v>-19.85566604000001</v>
+        <v>-20.3115724</v>
       </c>
       <c r="P91">
-        <v>-36.87480836000002</v>
+        <v>-37.72149160000001</v>
       </c>
       <c r="Q91">
-        <v>-18.87480836000002</v>
+        <v>-19.72149160000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.500965445930349</v>
+        <v>1.646481990523384</v>
       </c>
       <c r="T91">
-        <v>7.149769426857209</v>
+        <v>7.864746369542932</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1787278117098777</v>
+        <v>0.1767419471353235</v>
       </c>
       <c r="W91">
-        <v>0.1649114554086566</v>
+        <v>0.1653102170152271</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5106508905996505</v>
+        <v>0.5049769918152101</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3134273943660427</v>
+        <v>0.3513215741316477</v>
       </c>
       <c r="C92">
-        <v>-112.3902871669114</v>
+        <v>-173.3442729030571</v>
       </c>
       <c r="D92">
-        <v>439.1397128330886</v>
+        <v>384.6727270969429</v>
       </c>
       <c r="E92">
-        <v>317.23</v>
+        <v>323.717</v>
       </c>
       <c r="F92">
-        <v>583.83</v>
+        <v>590.317</v>
       </c>
       <c r="G92">
         <v>32.3</v>
@@ -8831,45 +8831,45 @@
         <v>59.2</v>
       </c>
       <c r="M92">
-        <v>117.233064</v>
+        <v>139.1967486</v>
       </c>
       <c r="N92">
-        <v>-58.03306400000001</v>
+        <v>-79.9967486</v>
       </c>
       <c r="O92">
-        <v>-20.3115724</v>
+        <v>-27.99886201</v>
       </c>
       <c r="P92">
-        <v>-37.72149160000001</v>
+        <v>-51.99788659000001</v>
       </c>
       <c r="Q92">
-        <v>-19.72149160000001</v>
+        <v>-33.99788659000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.646481990523384</v>
+        <v>1.874270875754927</v>
       </c>
       <c r="T92">
-        <v>7.864746369542932</v>
+        <v>8.983957942330873</v>
       </c>
       <c r="U92">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1767419471353235</v>
+        <v>0.1488540516096509</v>
       </c>
       <c r="W92">
-        <v>0.1653102170152271</v>
+        <v>0.2007002146304443</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y92">
-        <v>0.5049769918152101</v>
+        <v>0.4252972903132882</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3513215741316477</v>
+        <v>0.3532215741316477</v>
       </c>
       <c r="C93">
-        <v>-173.3442729030571</v>
+        <v>-182.2087188697192</v>
       </c>
       <c r="D93">
-        <v>384.6727270969429</v>
+        <v>382.2952811302808</v>
       </c>
       <c r="E93">
-        <v>323.717</v>
+        <v>330.2040000000001</v>
       </c>
       <c r="F93">
-        <v>590.317</v>
+        <v>596.8040000000001</v>
       </c>
       <c r="G93">
         <v>32.3</v>
@@ -8913,37 +8913,37 @@
         <v>59.2</v>
       </c>
       <c r="M93">
-        <v>139.1967486</v>
+        <v>140.7263832</v>
       </c>
       <c r="N93">
-        <v>-79.9967486</v>
+        <v>-81.52638320000001</v>
       </c>
       <c r="O93">
-        <v>-27.99886201</v>
+        <v>-28.53423412</v>
       </c>
       <c r="P93">
-        <v>-51.99788659000001</v>
+        <v>-52.99214908000001</v>
       </c>
       <c r="Q93">
-        <v>-33.99788659000001</v>
+        <v>-34.99214908000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.874270875754927</v>
+        <v>2.102829735224293</v>
       </c>
       <c r="T93">
-        <v>8.983957942330873</v>
+        <v>10.10695268512224</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1488540516096509</v>
+        <v>0.1472360727878068</v>
       </c>
       <c r="W93">
-        <v>0.2007002146304443</v>
+        <v>0.2010817340366352</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4252972903132882</v>
+        <v>0.4206744936794481</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3532215741316477</v>
+        <v>0.3551215741316477</v>
       </c>
       <c r="C94">
-        <v>-182.2087188697192</v>
+        <v>-191.0439580321075</v>
       </c>
       <c r="D94">
-        <v>382.2952811302808</v>
+        <v>379.9470419678925</v>
       </c>
       <c r="E94">
-        <v>330.2040000000001</v>
+        <v>336.691</v>
       </c>
       <c r="F94">
-        <v>596.8040000000001</v>
+        <v>603.2910000000001</v>
       </c>
       <c r="G94">
         <v>32.3</v>
@@ -8995,37 +8995,37 @@
         <v>59.2</v>
       </c>
       <c r="M94">
-        <v>140.7263832</v>
+        <v>142.2560178</v>
       </c>
       <c r="N94">
-        <v>-81.52638320000001</v>
+        <v>-83.05601780000002</v>
       </c>
       <c r="O94">
-        <v>-28.53423412</v>
+        <v>-29.06960623000001</v>
       </c>
       <c r="P94">
-        <v>-52.99214908000001</v>
+        <v>-53.98641157000002</v>
       </c>
       <c r="Q94">
-        <v>-34.99214908000001</v>
+        <v>-35.98641157000002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>2.102829735224293</v>
+        <v>2.396691125970621</v>
       </c>
       <c r="T94">
-        <v>10.10695268512224</v>
+        <v>11.55080306871113</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1472360727878068</v>
+        <v>0.1456528892094433</v>
       </c>
       <c r="W94">
-        <v>0.2010817340366352</v>
+        <v>0.2014550487244133</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4206744936794481</v>
+        <v>0.416151112026981</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3551215741316477</v>
+        <v>0.3570215741316477</v>
       </c>
       <c r="C95">
-        <v>-191.0439580321075</v>
+        <v>-199.8505253106718</v>
       </c>
       <c r="D95">
-        <v>379.9470419678925</v>
+        <v>377.6274746893283</v>
       </c>
       <c r="E95">
-        <v>336.691</v>
+        <v>343.1780000000001</v>
       </c>
       <c r="F95">
-        <v>603.2910000000001</v>
+        <v>609.7780000000001</v>
       </c>
       <c r="G95">
         <v>32.3</v>
@@ -9077,37 +9077,37 @@
         <v>59.2</v>
       </c>
       <c r="M95">
-        <v>142.2560178</v>
+        <v>143.7856524</v>
       </c>
       <c r="N95">
-        <v>-83.05601780000002</v>
+        <v>-84.58565240000003</v>
       </c>
       <c r="O95">
-        <v>-29.06960623000001</v>
+        <v>-29.60497834000001</v>
       </c>
       <c r="P95">
-        <v>-53.98641157000002</v>
+        <v>-54.98067406000002</v>
       </c>
       <c r="Q95">
-        <v>-35.98641157000002</v>
+        <v>-36.98067406000002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>2.396691125970621</v>
+        <v>2.788506313632392</v>
       </c>
       <c r="T95">
-        <v>11.55080306871113</v>
+        <v>13.47593691349632</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1456528892094433</v>
+        <v>0.1441033903880662</v>
       </c>
       <c r="W95">
-        <v>0.2014550487244133</v>
+        <v>0.201820420546494</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.416151112026981</v>
+        <v>0.4117239725373322</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3570215741316477</v>
+        <v>0.3589215741316478</v>
       </c>
       <c r="C96">
-        <v>-199.8505253106718</v>
+        <v>-208.6289426424206</v>
       </c>
       <c r="D96">
-        <v>377.6274746893283</v>
+        <v>375.3360573575795</v>
       </c>
       <c r="E96">
-        <v>343.1780000000001</v>
+        <v>349.6650000000001</v>
       </c>
       <c r="F96">
-        <v>609.7780000000001</v>
+        <v>616.2650000000001</v>
       </c>
       <c r="G96">
         <v>32.3</v>
@@ -9159,37 +9159,37 @@
         <v>59.2</v>
       </c>
       <c r="M96">
-        <v>143.7856524</v>
+        <v>145.315287</v>
       </c>
       <c r="N96">
-        <v>-84.58565240000003</v>
+        <v>-86.11528700000004</v>
       </c>
       <c r="O96">
-        <v>-29.60497834000001</v>
+        <v>-30.14035045000001</v>
       </c>
       <c r="P96">
-        <v>-54.98067406000002</v>
+        <v>-55.97493655000002</v>
       </c>
       <c r="Q96">
-        <v>-36.98067406000002</v>
+        <v>-37.97493655000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.788506313632392</v>
+        <v>3.337047576358872</v>
       </c>
       <c r="T96">
-        <v>13.47593691349632</v>
+        <v>16.17112429619559</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1441033903880662</v>
+        <v>0.1425865125945077</v>
       </c>
       <c r="W96">
-        <v>0.201820420546494</v>
+        <v>0.2021781003302151</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4117239725373322</v>
+        <v>0.4073900359843076</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3589215741316478</v>
+        <v>0.3608215741316477</v>
       </c>
       <c r="C97">
-        <v>-208.6289426424206</v>
+        <v>-217.3797193724592</v>
       </c>
       <c r="D97">
-        <v>375.3360573575795</v>
+        <v>373.0722806275408</v>
       </c>
       <c r="E97">
-        <v>349.6650000000001</v>
+        <v>356.152</v>
       </c>
       <c r="F97">
-        <v>616.2650000000001</v>
+        <v>622.7520000000001</v>
       </c>
       <c r="G97">
         <v>32.3</v>
@@ -9241,37 +9241,37 @@
         <v>59.2</v>
       </c>
       <c r="M97">
-        <v>145.315287</v>
+        <v>146.8449216</v>
       </c>
       <c r="N97">
-        <v>-86.11528700000004</v>
+        <v>-87.64492160000002</v>
       </c>
       <c r="O97">
-        <v>-30.14035045000001</v>
+        <v>-30.67572256</v>
       </c>
       <c r="P97">
-        <v>-55.97493655000002</v>
+        <v>-56.96919904000001</v>
       </c>
       <c r="Q97">
-        <v>-37.97493655000002</v>
+        <v>-38.96919904000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>3.337047576358872</v>
+        <v>4.159859470448592</v>
       </c>
       <c r="T97">
-        <v>16.17112429619559</v>
+        <v>20.2139053702445</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1425865125945077</v>
+        <v>0.1411012364216482</v>
       </c>
       <c r="W97">
-        <v>0.2021781003302151</v>
+        <v>0.2025283284517754</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4073900359843076</v>
+        <v>0.4031463897761378</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3608215741316477</v>
+        <v>0.3627215741316477</v>
       </c>
       <c r="C98">
-        <v>-217.3797193724592</v>
+        <v>-226.103352631443</v>
       </c>
       <c r="D98">
-        <v>373.0722806275408</v>
+        <v>370.835647368557</v>
       </c>
       <c r="E98">
-        <v>356.152</v>
+        <v>362.639</v>
       </c>
       <c r="F98">
-        <v>622.7520000000001</v>
+        <v>629.239</v>
       </c>
       <c r="G98">
         <v>32.3</v>
@@ -9323,37 +9323,37 @@
         <v>59.2</v>
       </c>
       <c r="M98">
-        <v>146.8449216</v>
+        <v>148.3745562</v>
       </c>
       <c r="N98">
-        <v>-87.64492160000002</v>
+        <v>-89.1745562</v>
       </c>
       <c r="O98">
-        <v>-30.67572256</v>
+        <v>-31.21109467</v>
       </c>
       <c r="P98">
-        <v>-56.96919904000001</v>
+        <v>-57.96346153</v>
       </c>
       <c r="Q98">
-        <v>-38.96919904000001</v>
+        <v>-39.96346153</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>4.159859470448581</v>
+        <v>5.531212627264773</v>
       </c>
       <c r="T98">
-        <v>20.21390537024444</v>
+        <v>26.95187382699259</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1411012364216482</v>
+        <v>0.1396465844997756</v>
       </c>
       <c r="W98">
-        <v>0.2025283284517754</v>
+        <v>0.2028713353749529</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4031463897761378</v>
+        <v>0.3989902414279303</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3627215741316477</v>
+        <v>0.3646215741316477</v>
       </c>
       <c r="C99">
-        <v>-226.103352631443</v>
+        <v>-234.8003276995333</v>
       </c>
       <c r="D99">
-        <v>370.835647368557</v>
+        <v>368.6256723004666</v>
       </c>
       <c r="E99">
-        <v>362.639</v>
+        <v>369.126</v>
       </c>
       <c r="F99">
-        <v>629.239</v>
+        <v>635.726</v>
       </c>
       <c r="G99">
         <v>32.3</v>
@@ -9405,37 +9405,37 @@
         <v>59.2</v>
       </c>
       <c r="M99">
-        <v>148.3745562</v>
+        <v>149.9041908</v>
       </c>
       <c r="N99">
-        <v>-89.1745562</v>
+        <v>-90.70419080000001</v>
       </c>
       <c r="O99">
-        <v>-31.21109467</v>
+        <v>-31.74646678</v>
       </c>
       <c r="P99">
-        <v>-57.96346153</v>
+        <v>-58.95772402000001</v>
       </c>
       <c r="Q99">
-        <v>-39.96346153</v>
+        <v>-40.95772402000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>5.531212627264773</v>
+        <v>8.273918940897161</v>
       </c>
       <c r="T99">
-        <v>26.95187382699259</v>
+        <v>40.42781074048889</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1396465844997756</v>
+        <v>0.1382216193518187</v>
       </c>
       <c r="W99">
-        <v>0.2028713353749529</v>
+        <v>0.2032073421568412</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3989902414279303</v>
+        <v>0.3949189124337676</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3646215741316477</v>
+        <v>0.3665215741316478</v>
       </c>
       <c r="C100">
-        <v>-234.8003276995333</v>
+        <v>-243.4711183574185</v>
       </c>
       <c r="D100">
-        <v>368.6256723004666</v>
+        <v>366.4418816425816</v>
       </c>
       <c r="E100">
-        <v>369.126</v>
+        <v>375.6130000000001</v>
       </c>
       <c r="F100">
-        <v>635.726</v>
+        <v>642.2130000000001</v>
       </c>
       <c r="G100">
         <v>32.3</v>
@@ -9487,37 +9487,37 @@
         <v>59.2</v>
       </c>
       <c r="M100">
-        <v>149.9041908</v>
+        <v>151.4338254</v>
       </c>
       <c r="N100">
-        <v>-90.70419080000001</v>
+        <v>-92.23382540000001</v>
       </c>
       <c r="O100">
-        <v>-31.74646678</v>
+        <v>-32.28183889</v>
       </c>
       <c r="P100">
-        <v>-58.95772402000001</v>
+        <v>-59.95198651000001</v>
       </c>
       <c r="Q100">
-        <v>-40.95772402000001</v>
+        <v>-41.95198651000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>8.273918940897161</v>
+        <v>16.50203788179433</v>
       </c>
       <c r="T100">
-        <v>40.42781074048889</v>
+        <v>80.85562148097779</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1382216193518187</v>
+        <v>0.1368254413785679</v>
       </c>
       <c r="W100">
-        <v>0.2032073421568412</v>
+        <v>0.2035365609229337</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3949189124337676</v>
+        <v>0.3909298325101942</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3665215741316478</v>
-      </c>
-      <c r="C101">
-        <v>-243.4711183574185</v>
-      </c>
-      <c r="D101">
-        <v>366.4418816425816</v>
-      </c>
-      <c r="E101">
-        <v>375.6130000000001</v>
-      </c>
-      <c r="F101">
-        <v>642.2130000000001</v>
-      </c>
-      <c r="G101">
-        <v>32.3</v>
-      </c>
-      <c r="H101">
-        <v>382.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>77.2</v>
-      </c>
-      <c r="K101">
-        <v>18</v>
-      </c>
-      <c r="L101">
-        <v>59.2</v>
-      </c>
-      <c r="M101">
-        <v>151.4338254</v>
-      </c>
-      <c r="N101">
-        <v>-92.23382540000001</v>
-      </c>
-      <c r="O101">
-        <v>-32.28183889</v>
-      </c>
-      <c r="P101">
-        <v>-59.95198651000001</v>
-      </c>
-      <c r="Q101">
-        <v>-41.95198651000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>16.50203788179433</v>
-      </c>
-      <c r="T101">
-        <v>80.85562148097779</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1368254413785679</v>
-      </c>
-      <c r="W101">
-        <v>0.2035365609229337</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3909298325101942</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
